--- a/src/attributions/attributions_saliency_traj_345.xlsx
+++ b/src/attributions/attributions_saliency_traj_345.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.001574121066369116</v>
+        <v>2.799124647345774e-11</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01283061318099499</v>
+        <v>5.764598520752173e-11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000215296953683719</v>
+        <v>1.616456100916874e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00490540498867631</v>
+        <v>5.08656797237883e-11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003110687248408794</v>
+        <v>5.952344866999582e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007914484478533268</v>
+        <v>6.057580825835629e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001289766980335116</v>
+        <v>2.384591656079404e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007793942000716925</v>
+        <v>2.3771750626983e-12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005506983026862144</v>
+        <v>6.488814346949923e-11</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003030807711184025</v>
+        <v>2.405149170103815e-11</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01184660010039806</v>
+        <v>1.098693080958668e-10</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001753754913806915</v>
+        <v>2.345260053868148e-12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009704355150461197</v>
+        <v>7.255675921191695e-11</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001105677802115679</v>
+        <v>1.015446615681981e-10</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005385288968682289</v>
+        <v>8.614210733615124e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003141327993944287</v>
+        <v>2.988768954548249e-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0009928271174430847</v>
+        <v>5.03749819635857e-11</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007025178521871567</v>
+        <v>5.350661233527454e-11</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001013093627989292</v>
+        <v>2.520658161364597e-11</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004354922566562891</v>
+        <v>3.613294559390301e-12</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001752172131091356</v>
+        <v>2.193130876557148e-12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0004308904753997922</v>
+        <v>4.125513472508224e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003555848728865385</v>
+        <v>2.252088619758563e-11</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004246488679200411</v>
+        <v>1.574313249208537e-11</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.000535080092959106</v>
+        <v>2.048448043134865e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.058247628156096e-05</v>
+        <v>1.028815834608343e-11</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.002557977102696896</v>
+        <v>1.428860415403355e-11</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.001821169396862388</v>
+        <v>2.204020993490374e-11</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0001259527634829283</v>
+        <v>2.761949176310896e-11</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.006937072612345219</v>
+        <v>5.192608842907731e-11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001855907961726189</v>
+        <v>7.249974232070855e-11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0008905584691092372</v>
+        <v>5.116790671721994e-11</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001878146314993501</v>
+        <v>2.89044612897249e-12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.002229158766567707</v>
+        <v>9.596632516428727e-12</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0006642951047979295</v>
+        <v>8.815850827126326e-11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0006677912315353751</v>
+        <v>5.574438133315596e-11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.002074107294902205</v>
+        <v>3.094143691262374e-11</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.000397723400965333</v>
+        <v>4.952209649300432e-12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001741852844133973</v>
+        <v>1.88164171743832e-11</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.291453610174358e-05</v>
+        <v>1.433737850664585e-11</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0006949148373678327</v>
+        <v>4.796132241358109e-11</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.002436345675960183</v>
+        <v>1.106980566240034e-11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0006737133953720331</v>
+        <v>4.593854463497138e-11</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.001631989376619458</v>
+        <v>2.664420984191396e-12</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.001307803904637694</v>
+        <v>1.562533262500221e-11</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0008252148982137442</v>
+        <v>1.207288956306396e-11</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.01342070568352938</v>
+        <v>1.705194319079339e-10</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.001790753100067377</v>
+        <v>1.152218294733776e-12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.001450574724003673</v>
+        <v>1.754934565723065e-11</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01304729096591473</v>
+        <v>6.35584640473752e-11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0005696818698197603</v>
+        <v>1.703991461821097e-11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.004045296460390091</v>
+        <v>2.005123497794692e-14</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.002201403258368373</v>
+        <v>2.512650330854793e-11</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.001559266587719321</v>
+        <v>3.354468092187091e-11</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0005516239325515926</v>
+        <v>1.385425021233067e-11</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0001151938922703266</v>
+        <v>3.798768244411832e-11</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.001330800238065422</v>
+        <v>3.468027297628962e-12</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.001059300964698195</v>
+        <v>7.266666435246094e-11</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.002791693899780512</v>
+        <v>6.721515705132575e-11</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.007411186117678881</v>
+        <v>9.137135492665038e-13</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.001553420093841851</v>
+        <v>1.406109603752093e-11</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.003734476864337921</v>
+        <v>1.892781417711653e-11</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.01060121972113848</v>
+        <v>6.364846150130887e-12</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0009017273550853133</v>
+        <v>2.72367232934112e-11</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.001899631228297949</v>
+        <v>5.301255961986939e-11</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001374444691464305</v>
+        <v>3.505796781350101e-12</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0003914579283446074</v>
+        <v>1.063519324689954e-11</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.01035700272768736</v>
+        <v>4.913654205740414e-11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0008239378221333027</v>
+        <v>4.067361031312444e-11</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.004171526059508324</v>
+        <v>6.932732860009949e-11</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.001503084786236286</v>
+        <v>1.88216456309398e-11</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.005340083967894316</v>
+        <v>3.413274871078009e-11</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0009553505224175751</v>
+        <v>7.344415874077637e-12</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.006188568659126759</v>
+        <v>6.562358989548045e-11</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.002550139557570219</v>
+        <v>1.362716710306966e-11</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0001889370614662766</v>
+        <v>1.764645027324541e-11</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.003380528884008527</v>
+        <v>4.757533950128234e-11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0003966169315390289</v>
+        <v>3.484768723582832e-11</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0001439480111002922</v>
+        <v>2.197307093221301e-11</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.002302663633599877</v>
+        <v>1.40892957023464e-11</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.004466482438147068</v>
+        <v>1.903163911187722e-11</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0003772115742322057</v>
+        <v>7.729246062626594e-12</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.001979667926207185</v>
+        <v>1.810352735776011e-11</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.001443556160666049</v>
+        <v>3.889862390527021e-12</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.0002672927803359926</v>
+        <v>3.283238611540007e-11</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0007871058769524097</v>
+        <v>1.555652828777454e-11</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0006185368401929736</v>
+        <v>2.679280408646179e-11</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.001298415707424283</v>
+        <v>2.143306192248229e-11</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.001441824482753873</v>
+        <v>3.233938724450658e-12</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.002103707753121853</v>
+        <v>2.054374032001149e-11</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.003721742192283273</v>
+        <v>4.939686853999703e-11</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.002693628892302513</v>
+        <v>9.520262356232934e-11</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.00040698132943362</v>
+        <v>9.996446379001434e-12</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.00612146407365799</v>
+        <v>4.825893851201357e-11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.006226575933396816</v>
+        <v>7.887404618323046e-11</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.004029534757137299</v>
+        <v>4.086124494318e-11</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.001547219115309417</v>
+        <v>7.307510499487968e-12</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.00448276661336422</v>
+        <v>2.196735415099793e-12</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.003289237152785063</v>
+        <v>1.049501197752933e-13</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0001164181958301924</v>
+        <v>1.951401193411861e-11</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.002209912519901991</v>
+        <v>2.006693249068103e-11</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0006367609021253884</v>
+        <v>4.362736300694836e-12</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0005303960060700774</v>
+        <v>2.676106038157489e-11</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0002841329551301897</v>
+        <v>5.530445892909519e-12</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0007194560021162033</v>
+        <v>2.845000797446762e-11</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.001373689505271614</v>
+        <v>1.042722852506728e-11</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0007713811937719584</v>
+        <v>1.435744058364552e-11</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.001548461499623954</v>
+        <v>2.185201672388892e-11</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.00142785906791687</v>
+        <v>2.050963218702684e-11</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.0002541746944189072</v>
+        <v>1.486265624461858e-11</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.003061522264033556</v>
+        <v>2.369322620043857e-12</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.0008581186411902308</v>
+        <v>1.140384748438139e-11</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.003756337333470583</v>
+        <v>2.122097983447979e-11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0008350084535777569</v>
+        <v>1.751460088073031e-11</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.0005746928509324789</v>
+        <v>3.631751843702347e-11</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.007256343495100737</v>
+        <v>1.1013669143356e-11</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0007498456398025155</v>
+        <v>1.010348228691615e-11</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.001767831156030297</v>
+        <v>8.416509676700823e-13</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0002654868876561522</v>
+        <v>2.678769966263372e-12</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.0009515676065348089</v>
+        <v>6.855358728602434e-12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0004606951551977545</v>
+        <v>6.850412598291555e-11</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.001947883632965386</v>
+        <v>2.224003273210151e-11</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.00107952393591404</v>
+        <v>3.754235117225946e-11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0002602750319056213</v>
+        <v>2.872069942982947e-11</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0005233496194705367</v>
+        <v>2.468387820531159e-11</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.003563682083040476</v>
+        <v>1.16807483824255e-11</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0001818913442548364</v>
+        <v>2.321864402132778e-11</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.004289743490517139</v>
+        <v>2.709635987807602e-11</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.001296810223720968</v>
+        <v>1.274161331998869e-12</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.002746190177276731</v>
+        <v>1.303300089378068e-11</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.002172803040593863</v>
+        <v>1.121450068225505e-11</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0040620774962008</v>
+        <v>3.356786029695691e-11</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.0008752448484301567</v>
+        <v>1.794377146868698e-11</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.004451028537005186</v>
+        <v>3.24211386903972e-11</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.002345161978155375</v>
+        <v>1.872403447567006e-11</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.001275482471100986</v>
+        <v>2.934366638562835e-11</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.002820203546434641</v>
+        <v>7.170745334322826e-12</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.00198851153254509</v>
+        <v>1.198349839498514e-11</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0009436284308321774</v>
+        <v>2.718972269555309e-11</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0009297916549257934</v>
+        <v>2.265791720912347e-11</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.00129336048848927</v>
+        <v>1.076934895427595e-11</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.002870994154363871</v>
+        <v>8.543405566330264e-12</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.001481876941397786</v>
+        <v>2.041458148360764e-11</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.002455269917845726</v>
+        <v>1.540293587121155e-11</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0008514870423823595</v>
+        <v>7.793527108390652e-12</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.001679128501564264</v>
+        <v>4.441128454574228e-12</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.001280787517316639</v>
+        <v>1.775293237069042e-12</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.001788325374945998</v>
+        <v>1.171264561034002e-11</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.002963053993880749</v>
+        <v>2.34696463652373e-11</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.001994406804442406</v>
+        <v>3.35117315841682e-11</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.001196941826492548</v>
+        <v>9.837027026282641e-12</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0021167928352952</v>
+        <v>3.030884224153318e-11</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.002014037221670151</v>
+        <v>1.916650171907008e-11</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0002482917916495353</v>
+        <v>1.685829253972315e-11</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.002758043352514505</v>
+        <v>2.554655792463834e-11</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0006528660305775702</v>
+        <v>6.015489755623049e-12</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.0007482448709197342</v>
+        <v>3.013460314615912e-11</v>
       </c>
       <c r="FB2" t="n">
-        <v>9.084271732717752e-05</v>
+        <v>9.578417052569232e-12</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0003118626191280782</v>
+        <v>2.328772591431161e-11</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.001486057415604591</v>
+        <v>1.455122741050863e-11</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.0007843931089155376</v>
+        <v>6.510258044462036e-12</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.001780877937562764</v>
+        <v>1.614279369899219e-11</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0002050485054496676</v>
+        <v>2.545156099764689e-11</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0003611025167629123</v>
+        <v>1.977404351372058e-11</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0007098731584846973</v>
+        <v>1.50097902856805e-12</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.002241994254291058</v>
+        <v>2.203257541688597e-11</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.006575555540621281</v>
+        <v>2.120940229000112e-11</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0009131922852247953</v>
+        <v>2.798756365551824e-11</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0005568123888224363</v>
+        <v>6.164172904749021e-13</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.001613645697943866</v>
+        <v>3.260048134223759e-11</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0006677415804006159</v>
+        <v>2.665468887275146e-11</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0007150273304432631</v>
+        <v>4.70579478162314e-11</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.003548532724380493</v>
+        <v>6.091682713815771e-11</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.003163706045597792</v>
+        <v>2.356364062205962e-11</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.002643927000463009</v>
+        <v>2.00071521849754e-11</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.005928764585405588</v>
+        <v>3.326739578257687e-11</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.001404371927492321</v>
+        <v>1.333526518376704e-11</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.004544662311673164</v>
+        <v>2.936430959499248e-11</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.001449739560484886</v>
+        <v>2.907522660133832e-11</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.001117082079872489</v>
+        <v>1.427230035544458e-11</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.001987122232094407</v>
+        <v>1.251912202376859e-11</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.001285334816202521</v>
+        <v>5.024526259465867e-13</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.00226702494546771</v>
+        <v>8.158033276695065e-12</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.002220259513705969</v>
+        <v>2.315909443384445e-11</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.001061174669303</v>
+        <v>4.431741432164849e-14</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.002185198478400707</v>
+        <v>2.431016152271148e-11</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.003045824123546481</v>
+        <v>8.115293159693948e-12</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.003842245321720839</v>
+        <v>1.969120873301922e-11</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.001245344174094498</v>
+        <v>2.372589277821469e-11</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001172357704490423</v>
+        <v>5.136960648521871e-11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06693115085363388</v>
+        <v>1.546716921208002e-11</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009387319907546043</v>
+        <v>2.632327515683652e-11</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02159618772566319</v>
+        <v>1.013629596924304e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008079968392848969</v>
+        <v>5.843599909516328e-12</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006092417053878307</v>
+        <v>1.870845318940884e-11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03672999143600464</v>
+        <v>5.417262471940631e-11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01323537435382605</v>
+        <v>1.253312592597311e-10</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005369295831769705</v>
+        <v>6.647799671855026e-11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006901382468640804</v>
+        <v>3.857865416012629e-11</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05513546615839005</v>
+        <v>3.621712998946869e-11</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01287798304110765</v>
+        <v>4.747605780730524e-11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03759892657399178</v>
+        <v>4.482406806838313e-11</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006470870226621628</v>
+        <v>3.893035893653973e-11</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01470199972391129</v>
+        <v>1.758305653853931e-11</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03162702545523643</v>
+        <v>5.951390075198404e-11</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0008519981056451797</v>
+        <v>1.160186738347058e-10</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008574234321713448</v>
+        <v>7.937970419868989e-11</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009773066267371178</v>
+        <v>5.430048771737361e-11</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01052549388259649</v>
+        <v>5.887463433440487e-11</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006448797881603241</v>
+        <v>1.706416605240513e-11</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0138755114749074</v>
+        <v>7.461237183647995e-11</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01405807305127382</v>
+        <v>4.350288358712096e-12</v>
       </c>
       <c r="X5" t="n">
-        <v>0.009277366101741791</v>
+        <v>2.2828692061716e-11</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003192812670022249</v>
+        <v>1.087680466527186e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.006842182949185371</v>
+        <v>1.066814280144268e-12</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004225818905979395</v>
+        <v>4.194906227938944e-11</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.007232533302158117</v>
+        <v>1.417473916021095e-10</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01913908496499062</v>
+        <v>7.836092191793043e-11</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.006604302674531937</v>
+        <v>4.319437862942976e-11</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.006953982170671225</v>
+        <v>9.135227296841464e-11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.004605826456099749</v>
+        <v>8.255209016372334e-11</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003695908468216658</v>
+        <v>1.161957075695996e-11</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.00182154995854944</v>
+        <v>1.93430479966672e-11</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.009801449254155159</v>
+        <v>4.222700661360435e-11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001171373995020986</v>
+        <v>2.792954929831115e-11</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.005201889201998711</v>
+        <v>1.670197140313245e-11</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.009025588631629944</v>
+        <v>1.070666732355674e-11</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.002134031150490046</v>
+        <v>2.880260266402423e-12</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.007472220342606306</v>
+        <v>6.602994540028106e-11</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.008361725136637688</v>
+        <v>5.001026676110243e-11</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.004379177000373602</v>
+        <v>6.606524355357024e-11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.004040548112243414</v>
+        <v>6.223323939513747e-11</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.003172555938363075</v>
+        <v>1.214044316466545e-11</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.006997399963438511</v>
+        <v>4.444564161154574e-11</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.01014943700283766</v>
+        <v>8.550798957784878e-13</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04354226961731911</v>
+        <v>1.197798665808492e-10</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.005111258011311293</v>
+        <v>2.798795570302381e-11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.01752638071775436</v>
+        <v>4.706800921239207e-11</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.01810887828469276</v>
+        <v>7.397252255181286e-11</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.004349438473582268</v>
+        <v>1.068074031995714e-10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.02603588253259659</v>
+        <v>2.199806482805489e-11</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.003139931242913008</v>
+        <v>1.448945824433778e-11</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001888839527964592</v>
+        <v>3.206744245143334e-11</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0005383375100791454</v>
+        <v>4.569442046964411e-12</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01462642941623926</v>
+        <v>1.766679164072471e-11</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.01530259102582932</v>
+        <v>4.363138322860394e-11</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.01292138267308474</v>
+        <v>5.462063787375904e-11</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.02002231404185295</v>
+        <v>1.155907244920762e-10</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.003770665265619755</v>
+        <v>8.509421639546488e-11</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0009685107506811619</v>
+        <v>6.597043050726725e-11</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.005186725873500109</v>
+        <v>6.867992979886495e-11</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0079534025862813</v>
+        <v>1.725605769387073e-10</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.00686250627040863</v>
+        <v>7.14625233988464e-12</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.007756630890071392</v>
+        <v>4.533054834277017e-11</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.978893462568521e-06</v>
+        <v>2.959745296071681e-11</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.01014660857617855</v>
+        <v>6.882930857210479e-12</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01440739538520575</v>
+        <v>8.247215410595032e-11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.006080809514969587</v>
+        <v>1.601123747474453e-13</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.01291905343532562</v>
+        <v>6.428725607410257e-11</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.02220995910465717</v>
+        <v>4.653317661751366e-11</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.003534037154167891</v>
+        <v>5.920650688467921e-12</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.002609133487567306</v>
+        <v>4.105087103578597e-11</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01796664483845234</v>
+        <v>2.03026727374489e-11</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.01019964087754488</v>
+        <v>3.604152740144251e-11</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.01040681824088097</v>
+        <v>6.972397659232854e-11</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.008344945497810841</v>
+        <v>3.656510857985573e-11</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.005797567777335644</v>
+        <v>3.243811469433311e-12</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.01338533870875835</v>
+        <v>1.168767443937568e-10</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.009503265842795372</v>
+        <v>1.04208291301644e-11</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0006604808149859309</v>
+        <v>1.268126575970641e-11</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001241136342287064</v>
+        <v>3.316471229586337e-12</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.01096841879189014</v>
+        <v>3.920466729034899e-11</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.003755320329219103</v>
+        <v>3.6237398498562e-11</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.002633587922900915</v>
+        <v>2.07021691456255e-11</v>
       </c>
       <c r="CH5" t="n">
-        <v>6.892101373523474e-05</v>
+        <v>4.262859162884602e-12</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001457020523957908</v>
+        <v>4.79555804788756e-12</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.008453796617686749</v>
+        <v>1.041929303252642e-11</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.00153175019659102</v>
+        <v>3.98525938812011e-13</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0001814014976844192</v>
+        <v>3.809604541549216e-13</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.01196124590933323</v>
+        <v>7.207730245983868e-11</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004547770600765944</v>
+        <v>1.220301776294619e-10</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001430165488272905</v>
+        <v>5.803105912471906e-11</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.02064942568540573</v>
+        <v>6.648760014771327e-11</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.012424411252141</v>
+        <v>1.012344305606483e-10</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001494251424446702</v>
+        <v>1.763823982703361e-11</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001141400774940848</v>
+        <v>3.374692886248809e-11</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.002950129099190235</v>
+        <v>5.102781044930005e-11</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0008706632070243359</v>
+        <v>6.844647765236189e-11</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0007581691606901586</v>
+        <v>9.565907094222226e-12</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.01105070486664772</v>
+        <v>1.231760613645827e-11</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.00329759786836803</v>
+        <v>4.410013326738849e-11</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.008643456734716892</v>
+        <v>1.791055671829245e-11</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.003351611783728004</v>
+        <v>1.704609023378545e-11</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.001655799685977399</v>
+        <v>6.385040933476471e-12</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.009365624748170376</v>
+        <v>7.189281722025376e-12</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001626279437914491</v>
+        <v>4.083843940100307e-12</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0001541413366794586</v>
+        <v>9.495190224362293e-12</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.006891562603414059</v>
+        <v>2.456390646443651e-11</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.001946935779415071</v>
+        <v>1.709088079393517e-11</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0001295168185606599</v>
+        <v>1.568893071013377e-10</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.00562286889180541</v>
+        <v>1.535345184322523e-10</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001974896993488073</v>
+        <v>8.303172732704311e-11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001359441783279181</v>
+        <v>6.059087259702167e-11</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0009279849473387003</v>
+        <v>1.149892611684855e-10</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.01588906534016132</v>
+        <v>7.949611455226879e-12</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.003847536630928516</v>
+        <v>6.284616924090436e-13</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.01241239532828331</v>
+        <v>3.82099976659056e-11</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.004770449362695217</v>
+        <v>1.767004598196564e-11</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.004671640694141388</v>
+        <v>2.371128814127044e-11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.009388542734086514</v>
+        <v>1.069598055958298e-11</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.005909938365221024</v>
+        <v>6.085417586509934e-11</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.00317670963704586</v>
+        <v>2.668765555768893e-11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.007544017862528563</v>
+        <v>6.493809656671345e-11</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.002244319999590516</v>
+        <v>4.621435178986388e-11</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.00363961374387145</v>
+        <v>4.064266631575997e-11</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0006774978246539831</v>
+        <v>3.560364850163644e-11</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01870610192418098</v>
+        <v>1.579122388406518e-10</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.00350695219822228</v>
+        <v>5.493413363089061e-11</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.007012700196355581</v>
+        <v>8.714730326264686e-11</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01140737812966108</v>
+        <v>6.987552897408378e-14</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0005635521374642849</v>
+        <v>5.645070522142248e-11</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0004500788636505604</v>
+        <v>4.337169165480326e-11</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.008326325565576553</v>
+        <v>3.393520187078281e-11</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.006255027838051319</v>
+        <v>6.58797669195188e-11</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.002424725797027349</v>
+        <v>1.268114502295248e-10</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.00924320612102747</v>
+        <v>5.379956202755665e-11</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.002467503771185875</v>
+        <v>4.189428665091199e-11</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.003123348113149405</v>
+        <v>1.492000967218132e-12</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.002732884837314487</v>
+        <v>5.950569897938962e-13</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0004948620917275548</v>
+        <v>3.5569380774092e-11</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.01380978059023619</v>
+        <v>4.847880083480582e-11</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0007672676583752036</v>
+        <v>8.773936438499774e-12</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.003237309399992228</v>
+        <v>8.550484972835726e-12</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.008287223055958748</v>
+        <v>2.173962052043343e-11</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.006258659996092319</v>
+        <v>4.222094028560885e-12</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.007147941738367081</v>
+        <v>3.255032701710014e-11</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.008548850193619728</v>
+        <v>1.583362607693317e-11</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01583980023860931</v>
+        <v>5.087109206103335e-11</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0002622706815600395</v>
+        <v>4.063391290110019e-11</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.006336198654025793</v>
+        <v>4.136044284841489e-11</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.008683210238814354</v>
+        <v>4.726110475195e-11</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.004306582733988762</v>
+        <v>4.33558744461493e-11</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.002929628826677799</v>
+        <v>1.143850639206967e-12</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.01179408468306065</v>
+        <v>3.567774548018932e-11</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.001764613320119679</v>
+        <v>4.140793263829323e-11</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.004769600462168455</v>
+        <v>2.78843129142281e-11</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.004392774775624275</v>
+        <v>2.487609250534373e-11</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0004240261623635888</v>
+        <v>1.439186790574976e-11</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.01002305932343006</v>
+        <v>1.942598425869191e-12</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.002929855370894074</v>
+        <v>2.892962345374395e-12</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001798887969926</v>
+        <v>1.136543810453805e-11</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.007990024052560329</v>
+        <v>2.911133140104383e-11</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0007024339865893126</v>
+        <v>9.147450852342587e-11</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.008137313649058342</v>
+        <v>1.764802193271464e-11</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.003210714086890221</v>
+        <v>1.290568520107005e-11</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01880293339490891</v>
+        <v>4.187009419731602e-11</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.005294024478644133</v>
+        <v>6.290345327952807e-11</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.001673321821726859</v>
+        <v>1.790776901766655e-11</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.005409345030784607</v>
+        <v>8.083980013173786e-11</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.01142567954957485</v>
+        <v>1.153359630023942e-10</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.01201874949038029</v>
+        <v>4.305873713139619e-11</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.01627491228282452</v>
+        <v>1.761428641833263e-10</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.004424181301146746</v>
+        <v>8.642590115792714e-11</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.009749465622007847</v>
+        <v>8.695190401031283e-12</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01724802330136299</v>
+        <v>6.858408285737028e-11</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.008161251433193684</v>
+        <v>5.731225563576636e-11</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.00232964102178812</v>
+        <v>8.388965910821611e-11</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.01799573749303818</v>
+        <v>1.90184978876573e-10</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.004964374471455812</v>
+        <v>1.086730636035149e-10</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.01322937570512295</v>
+        <v>1.680687186644825e-11</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.004579265136271715</v>
+        <v>4.718538060277666e-12</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0006707663414999843</v>
+        <v>7.001129537220763e-11</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0006175105227157474</v>
+        <v>7.056671913474588e-11</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.007178516127169132</v>
+        <v>7.464880102947546e-11</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.01037410646677017</v>
+        <v>3.655581393147145e-11</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.01531719509512186</v>
+        <v>3.638376058767712e-12</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.01534591242671013</v>
+        <v>2.097164976400112e-11</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.002532350597903132</v>
+        <v>5.589959051199855e-11</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.03280035406351089</v>
+        <v>0.140199214220047</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2579551935195923</v>
+        <v>0.500637412071228</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005899995565414429</v>
+        <v>0.1614375412464142</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1839301586151123</v>
+        <v>0.1188929080963135</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01305210031569004</v>
+        <v>0.01799710467457771</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02441832982003689</v>
+        <v>0.1582376062870026</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03228306770324707</v>
+        <v>0.2058702111244202</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02011296153068542</v>
+        <v>0.1151556149125099</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06334835290908813</v>
+        <v>0.1544098407030106</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05423479899764061</v>
+        <v>0.08966736495494843</v>
       </c>
       <c r="K7" t="n">
-        <v>0.225669264793396</v>
+        <v>0.65690016746521</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006589337252080441</v>
+        <v>0.2113341093063354</v>
       </c>
       <c r="M7" t="n">
-        <v>0.179572731256485</v>
+        <v>0.1675413101911545</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06361669301986694</v>
+        <v>0.03712794929742813</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02210242487490177</v>
+        <v>0.1335094273090363</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01776811480522156</v>
+        <v>0.1555196195840836</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03615542501211166</v>
+        <v>0.3166419565677643</v>
       </c>
       <c r="R7" t="n">
-        <v>0.04996722191572189</v>
+        <v>0.1462139785289764</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01021808944642544</v>
+        <v>0.01168705150485039</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02916213870048523</v>
+        <v>0.08601468056440353</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01737632602453232</v>
+        <v>0.1133703589439392</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003280132077634335</v>
+        <v>0.05064563453197479</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03466355055570602</v>
+        <v>0.07317632436752319</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01505761500447989</v>
+        <v>0.09021683037281036</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03887719660997391</v>
+        <v>0.002021054737269878</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02643635123968124</v>
+        <v>0.02251183427870274</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02174124866724014</v>
+        <v>0.1227956786751747</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05664186552166939</v>
+        <v>0.08390737324953079</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02757135406136513</v>
+        <v>0.001160584390163422</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001785983331501484</v>
+        <v>0.02970747649669647</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0324469730257988</v>
+        <v>0.2404762506484985</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03627132624387741</v>
+        <v>0.04106462746858597</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0443720817565918</v>
+        <v>0.1947942674160004</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01468455232679844</v>
+        <v>0.05955887585878372</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.03465851023793221</v>
+        <v>0.03067884035408497</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.006576564162969589</v>
+        <v>0.007780697196722031</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01028707157820463</v>
+        <v>0.01095573790371418</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.009806257672607899</v>
+        <v>0.1928398907184601</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004778685048222542</v>
+        <v>0.07384544610977173</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.006557697895914316</v>
+        <v>0.05733368545770645</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.01552107371389866</v>
+        <v>0.1517971307039261</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.005690316669642925</v>
+        <v>0.04777438193559647</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01883725449442863</v>
+        <v>0.03280277922749519</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.009580818936228752</v>
+        <v>0.02402237057685852</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.006947836373001337</v>
+        <v>0.005722873844206333</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.05462890118360519</v>
+        <v>0.0336611270904541</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.148397296667099</v>
+        <v>0.3593766093254089</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0429425910115242</v>
+        <v>0.1033734753727913</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.04259981215000153</v>
+        <v>0.1352669894695282</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.005313192028552294</v>
+        <v>0.1346213072538376</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.03017324954271317</v>
+        <v>0.04204999655485153</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0002703315112739801</v>
+        <v>0.04588989168405533</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.03301824629306793</v>
+        <v>0.009033864364027977</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.002038866281509399</v>
+        <v>0.02112614177167416</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.02191178500652313</v>
+        <v>0.1398068815469742</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.06073996424674988</v>
+        <v>0.09847540408372879</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0446665994822979</v>
+        <v>0.2122563123703003</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0362822599709034</v>
+        <v>0.1158831864595413</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.04916655272245407</v>
+        <v>0.1900823712348938</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006289934739470482</v>
+        <v>0.147303968667984</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.03032000549137592</v>
+        <v>0.03273699805140495</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.04063704609870911</v>
+        <v>0.1400764584541321</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02972430363297462</v>
+        <v>0.1681850403547287</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.03748960793018341</v>
+        <v>0.009364288300275803</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.004914642311632633</v>
+        <v>0.1143227815628052</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0004262347356416285</v>
+        <v>0.03258059173822403</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.02047552727162838</v>
+        <v>0.01776603609323502</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.03652786836028099</v>
+        <v>0.03716506063938141</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02492925524711609</v>
+        <v>0.0111392866820097</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001631693681702018</v>
+        <v>0.03818795084953308</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.03613491356372833</v>
+        <v>0.005013581365346909</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.007840849459171295</v>
+        <v>0.006978961639106274</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.02574800886213779</v>
+        <v>0.03743249922990799</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.07929052412509918</v>
+        <v>0.2771300673484802</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01580505259335041</v>
+        <v>0.02689832635223866</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01798216253519058</v>
+        <v>0.03754246234893799</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.02053910866379738</v>
+        <v>0.01988442614674568</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.01091351825743914</v>
+        <v>0.06860315054655075</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.01809635385870934</v>
+        <v>0.01968380622565746</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.008189918473362923</v>
+        <v>0.08729039877653122</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.007969243451952934</v>
+        <v>0.08533001691102982</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.01016633957624435</v>
+        <v>0.003173303790390491</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.03870668262243271</v>
+        <v>0.174391895532608</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0150371827185154</v>
+        <v>0.06277993321418762</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02126608975231647</v>
+        <v>0.07102888822555542</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.008956854231655598</v>
+        <v>0.04845218360424042</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.005382084287703037</v>
+        <v>0.01306203007698059</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.007711263839155436</v>
+        <v>0.02653011865913868</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.004558922257274389</v>
+        <v>0.01798084005713463</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.01453664526343346</v>
+        <v>0.02047071978449821</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.05942883715033531</v>
+        <v>0.03609967604279518</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.009702298790216446</v>
+        <v>0.1523273885250092</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0006249092984944582</v>
+        <v>0.08691705763339996</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.05916963890194893</v>
+        <v>0.2955345213413239</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.03977994620800018</v>
+        <v>0.178214892745018</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.00436397735029459</v>
+        <v>0.0273628756403923</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.03172486275434494</v>
+        <v>0.1120735257863998</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.02958502061665058</v>
+        <v>0.0008637867867946625</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.007444247603416443</v>
+        <v>0.07340261340141296</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.006795509252697229</v>
+        <v>0.01018081977963448</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.03394464030861855</v>
+        <v>0.1757827699184418</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.02011124975979328</v>
+        <v>0.05674372613430023</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.02770957536995411</v>
+        <v>0.07073366641998291</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.01629592664539814</v>
+        <v>0.03317643329501152</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.005609096027910709</v>
+        <v>0.02010260336101055</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01022866368293762</v>
+        <v>0.01997263543307781</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.002371031092479825</v>
+        <v>0.0107095567509532</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01204157620668411</v>
+        <v>0.0442819856107235</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.01295418944209814</v>
+        <v>0.0121163222938776</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.001444365712814033</v>
+        <v>0.145338237285614</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0351104624569416</v>
+        <v>0.1162499114871025</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.07412131875753403</v>
+        <v>0.04817061126232147</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.01843683794140816</v>
+        <v>0.09764071553945541</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.02780023403465748</v>
+        <v>0.1887317448854446</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.02269487455487251</v>
+        <v>0.01150809228420258</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.01669849827885628</v>
+        <v>0.1654625535011292</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.04468012601137161</v>
+        <v>0.03076540678739548</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.01531229075044394</v>
+        <v>0.009013775736093521</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.00606698589399457</v>
+        <v>0.04912148788571358</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.00912605132907629</v>
+        <v>0.01261960528790951</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.02938880585134029</v>
+        <v>0.03362707048654556</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.03814912587404251</v>
+        <v>0.001115389168262482</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.01924146898090839</v>
+        <v>0.07715506106615067</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.005039828363806009</v>
+        <v>0.006015453487634659</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.02689541131258011</v>
+        <v>0.01292892266064882</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0147186117246747</v>
+        <v>0.1571755409240723</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.01012526080012321</v>
+        <v>0.04685194045305252</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.002694903407245874</v>
+        <v>0.1135692894458771</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.01407313719391823</v>
+        <v>0.05895804986357689</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.03359592333436012</v>
+        <v>0.09925465285778046</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01658331975340843</v>
+        <v>0.0883968323469162</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.008024083450436592</v>
+        <v>0.07823392003774643</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.01270135492086411</v>
+        <v>0.05135415121912956</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.002132072346284986</v>
+        <v>0.1189954280853271</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.009640722535550594</v>
+        <v>0.1213921755552292</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.003539362922310829</v>
+        <v>0.03233704343438148</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.04219716787338257</v>
+        <v>0.1381020992994308</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.02672774158418179</v>
+        <v>0.02545198053121567</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02224940434098244</v>
+        <v>0.03179270774126053</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01581643149256706</v>
+        <v>0.02767419815063477</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.009969605132937431</v>
+        <v>0.0206910353153944</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.01250654458999634</v>
+        <v>0.001300172880291939</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.006384748965501785</v>
+        <v>0.009718619287014008</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.007944749668240547</v>
+        <v>0.0121822627261281</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.004169379826635122</v>
+        <v>0.01327071152627468</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.02835727483034134</v>
+        <v>0.1149888709187508</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.03618169203400612</v>
+        <v>0.01272532902657986</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.01315901521593332</v>
+        <v>0.02608595415949821</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.007041111588478088</v>
+        <v>0.06433346122503281</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0100855240598321</v>
+        <v>0.0045278649777174</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.02147027291357517</v>
+        <v>0.05345939472317696</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.03187396749854088</v>
+        <v>0.03979693725705147</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.004882521461695433</v>
+        <v>0.07019970566034317</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.002141084522008896</v>
+        <v>0.003655224107205868</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.03566772490739822</v>
+        <v>0.1979248374700546</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.01409597601741552</v>
+        <v>0.03856169059872627</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02073032036423683</v>
+        <v>0.0847492516040802</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01272554136812687</v>
+        <v>0.03062046691775322</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.00770673668012023</v>
+        <v>0.01755451411008835</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.009010883048176765</v>
+        <v>0.01010295934975147</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0001390380784869194</v>
+        <v>0.02871940284967422</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01923237554728985</v>
+        <v>0.04263382405042648</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.01133534871041775</v>
+        <v>0.0258796364068985</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0249972939491272</v>
+        <v>0.08580777049064636</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.02129686996340752</v>
+        <v>0.08857422322034836</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03155066817998886</v>
+        <v>0.07792439311742783</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.005589243490248919</v>
+        <v>0.08661846816539764</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.04872716218233109</v>
+        <v>0.07238569855690002</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.01446969248354435</v>
+        <v>0.06175973638892174</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.008813846856355667</v>
+        <v>0.009889055043458939</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.02248254045844078</v>
+        <v>0.1257481426000595</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.004090254195034504</v>
+        <v>0.1020646765828133</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.04923146218061447</v>
+        <v>0.1525190472602844</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.02095050923526287</v>
+        <v>0.03422852233052254</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.03010198473930359</v>
+        <v>0.06076968088746071</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02086017839610577</v>
+        <v>0.167075589299202</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.008532754145562649</v>
+        <v>0.03372197598218918</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.008204535581171513</v>
+        <v>0.02139070443809032</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.004288826137781143</v>
+        <v>0.002031687647104263</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.03985657542943954</v>
+        <v>0.07743139564990997</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.05317580699920654</v>
+        <v>0.01489130966365337</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.01521414518356323</v>
+        <v>0.1904169619083405</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.01694888062775135</v>
+        <v>0.03895913064479828</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.01953768730163574</v>
+        <v>0.02894268743693829</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.05941043049097061</v>
+        <v>0.03181438893079758</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.05057359486818314</v>
+        <v>0.0246061347424984</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.06533278524875641</v>
+        <v>0.1204822212457657</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0101487971842289</v>
+        <v>0.03027962520718575</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01808490231633186</v>
+        <v>0.001197534147650003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.05457844212651253</v>
+        <v>0.3877325057983398</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3756232857704163</v>
+        <v>1.055076479911804</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03033032268285751</v>
+        <v>0.007298864424228668</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2345129102468491</v>
+        <v>0.3035154044628143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0634068176150322</v>
+        <v>0.2225298583507538</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2796862125396729</v>
+        <v>0.5044354200363159</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01533949188888073</v>
+        <v>0.1012895479798317</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08798658847808838</v>
+        <v>0.1603152900934219</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04689948260784149</v>
+        <v>0.1220521181821823</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1229396834969521</v>
+        <v>0.260530024766922</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2906569242477417</v>
+        <v>1.246171116828918</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01113436929881573</v>
+        <v>0.1407012641429901</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2099158614873886</v>
+        <v>0.6451226472854614</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04510417953133583</v>
+        <v>0.05276528000831604</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3171952962875366</v>
+        <v>0.4053193926811218</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003111096099019051</v>
+        <v>0.07153677940368652</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01028158515691757</v>
+        <v>0.02069347351789474</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0483822226524353</v>
+        <v>0.0846182256937027</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03576239943504333</v>
+        <v>0.009125359356403351</v>
       </c>
       <c r="T8" t="n">
-        <v>0.05358003824949265</v>
+        <v>0.1686179935932159</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03973409906029701</v>
+        <v>0.06401535868644714</v>
       </c>
       <c r="V8" t="n">
-        <v>0.04847288504242897</v>
+        <v>0.1190735399723053</v>
       </c>
       <c r="W8" t="n">
-        <v>0.02397040650248528</v>
+        <v>0.08385604619979858</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02149491012096405</v>
+        <v>0.03365276008844376</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.05130007117986679</v>
+        <v>0.1449743360280991</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03464151918888092</v>
+        <v>0.2211214154958725</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.04685020074248314</v>
+        <v>0.08178810030221939</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.003164010122418404</v>
+        <v>0.00698780408129096</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03682489320635796</v>
+        <v>0.08908902108669281</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01880984753370285</v>
+        <v>0.1089683398604393</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.004202829208225012</v>
+        <v>0.3179737329483032</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01431651599705219</v>
+        <v>0.2596381008625031</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.003874869085848331</v>
+        <v>0.08375890552997589</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.02461028657853603</v>
+        <v>0.09336498379707336</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03200426697731018</v>
+        <v>0.4373735189437866</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0341029018163681</v>
+        <v>0.1479171812534332</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.03619958832859993</v>
+        <v>0.003100782632827759</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.06743139028549194</v>
+        <v>0.1984577178955078</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0231385100632906</v>
+        <v>0.09442505240440369</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002757499925792217</v>
+        <v>0.01077200844883919</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.02291881665587425</v>
+        <v>0.1650742739439011</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0453488677740097</v>
+        <v>0.2472557425498962</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.006613964680582285</v>
+        <v>0.1437460035085678</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.03217770904302597</v>
+        <v>0.3478653430938721</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.05552578344941139</v>
+        <v>0.02844538912177086</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.02772539854049683</v>
+        <v>0.1318234354257584</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2406556606292725</v>
+        <v>1.019747972488403</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.02018558979034424</v>
+        <v>0.02844339236617088</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.04015438258647919</v>
+        <v>0.03652544319629669</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.04253765940666199</v>
+        <v>0.22742860019207</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.1426982432603836</v>
+        <v>0.4553937911987305</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.01777143403887749</v>
+        <v>0.05085119605064392</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.04464329034090042</v>
+        <v>0.03993816301226616</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.08129778504371643</v>
+        <v>0.07525121420621872</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.06491909921169281</v>
+        <v>0.06253994256258011</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.06595359742641449</v>
+        <v>0.02790990099310875</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.1089368686079979</v>
+        <v>0.08643623441457748</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.07144185155630112</v>
+        <v>0.2414354979991913</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.09441772103309631</v>
+        <v>0.09836786985397339</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.07702707499265671</v>
+        <v>0.2133330404758453</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01157144643366337</v>
+        <v>0.009030215442180634</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.05949734151363373</v>
+        <v>0.06877908110618591</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.03789833560585976</v>
+        <v>0.05759349837899208</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.01199036557227373</v>
+        <v>0.0819675624370575</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04305504634976387</v>
+        <v>0.08064573258161545</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.04697418585419655</v>
+        <v>0.00661779846996069</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.04880088940262794</v>
+        <v>0.1219285279512405</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0252128466963768</v>
+        <v>0.1423798054456711</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.003847848856821656</v>
+        <v>0.03190970048308372</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.02180861122906208</v>
+        <v>0.1017525494098663</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.02461914345622063</v>
+        <v>0.05489629507064819</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.01277627609670162</v>
+        <v>0.04017665982246399</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.02563236653804779</v>
+        <v>0.04255672544240952</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1163399592041969</v>
+        <v>0.7052946090698242</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.05812428146600723</v>
+        <v>0.08323994278907776</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.07928436994552612</v>
+        <v>0.1201839596033096</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.04888933524489403</v>
+        <v>0.02406921982765198</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.05792932212352753</v>
+        <v>0.2443963140249252</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.02540765888988972</v>
+        <v>0.1833764761686325</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.02788450382649899</v>
+        <v>0.09615471959114075</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.06180310994386673</v>
+        <v>0.05428043752908707</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.007952975109219551</v>
+        <v>0.07442223280668259</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0570480078458786</v>
+        <v>0.2981519103050232</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.05573854222893715</v>
+        <v>0.006423084530979395</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.03927101939916611</v>
+        <v>0.1156138777732849</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.01953767240047455</v>
+        <v>0.04949132353067398</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.05299118533730507</v>
+        <v>0.1457088142633438</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.01743324100971222</v>
+        <v>0.02947567217051983</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.01782448217272758</v>
+        <v>0.01975550875067711</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0330570787191391</v>
+        <v>0.02510374411940575</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.04176101833581924</v>
+        <v>0.2800260484218597</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01112117804586887</v>
+        <v>0.5565202236175537</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0171076525002718</v>
+        <v>0.142804816365242</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.002501560375094414</v>
+        <v>0.1709267646074295</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.02368350327014923</v>
+        <v>0.1912868022918701</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.008406748063862324</v>
+        <v>0.3616000115871429</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.05154208093881607</v>
+        <v>0.003949061036109924</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.05397816747426987</v>
+        <v>0.01055276021361351</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.02523364499211311</v>
+        <v>0.004058465361595154</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.001497677527368069</v>
+        <v>0.005357019603252411</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.05205310508608818</v>
+        <v>0.2956524789333344</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.05036782473325729</v>
+        <v>0.005771690979599953</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0566357895731926</v>
+        <v>0.09919076412916183</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01338917575776577</v>
+        <v>0.08048158884048462</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.06164043396711349</v>
+        <v>0.126460075378418</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.01668207347393036</v>
+        <v>0.03741198405623436</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0389118567109108</v>
+        <v>0.00828530453145504</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.01706108264625072</v>
+        <v>0.05728276073932648</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.03620408475399017</v>
+        <v>0.3401775658130646</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.02633428946137428</v>
+        <v>0.03714251518249512</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.01734518446028233</v>
+        <v>0.09286133944988251</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.1200615391135216</v>
+        <v>0.1908269077539444</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.008102457970380783</v>
+        <v>0.2644320130348206</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.05493876338005066</v>
+        <v>0.1852776110172272</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.02371705882251263</v>
+        <v>0.1027581393718719</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.03509920462965965</v>
+        <v>0.01136466488242149</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.003570393659174442</v>
+        <v>0.1127173453569412</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.008960703387856483</v>
+        <v>0.1107577607035637</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.00413492089137435</v>
+        <v>0.1027274131774902</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.02526364289224148</v>
+        <v>0.08478490263223648</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.04190965741872787</v>
+        <v>0.190603107213974</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0166858434677124</v>
+        <v>0.02644806727766991</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01827895641326904</v>
+        <v>0.004310110583901405</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.050902359187603</v>
+        <v>0.09243230521678925</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.003883205354213715</v>
+        <v>0.1490112841129303</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0766669288277626</v>
+        <v>0.002751275897026062</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.01705084554851055</v>
+        <v>0.1210717409849167</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02630777284502983</v>
+        <v>0.1428465396165848</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.07657863944768906</v>
+        <v>0.08578874170780182</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.005190829280763865</v>
+        <v>0.01365341246128082</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.006334889214485884</v>
+        <v>0.1806470900774002</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.03182429820299149</v>
+        <v>0.06054101139307022</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.009207927621901035</v>
+        <v>0.02304620668292046</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.04018684849143028</v>
+        <v>0.1846010386943817</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.03279417753219604</v>
+        <v>0.2459036856889725</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.02594790235161781</v>
+        <v>0.04563542455434799</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.04459322616457939</v>
+        <v>0.06729196012020111</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.03917503729462624</v>
+        <v>0.01663899049162865</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.007517899386584759</v>
+        <v>0.1685172766447067</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.003479829989373684</v>
+        <v>0.1574278920888901</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.07317104190587997</v>
+        <v>0.01437873765826225</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.017808448523283</v>
+        <v>0.004796524532139301</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.002942110178992152</v>
+        <v>0.06041787937283516</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.01000607758760452</v>
+        <v>0.07026053965091705</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0005208402872085571</v>
+        <v>0.04672268778085709</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.01982064545154572</v>
+        <v>0.1486646980047226</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.05501390248537064</v>
+        <v>0.07921279966831207</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.02689535170793533</v>
+        <v>0.04216412454843521</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.01891452819108963</v>
+        <v>0.3523217439651489</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.04267245158553123</v>
+        <v>0.1123359426856041</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.03654268383979797</v>
+        <v>0.003448463976383209</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.07635681331157684</v>
+        <v>0.07475695759057999</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.008555658161640167</v>
+        <v>0.05717793107032776</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.004427297506481409</v>
+        <v>0.03363185375928879</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.04936835542321205</v>
+        <v>0.3396100699901581</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.04201489314436913</v>
+        <v>0.001033877953886986</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.05198299139738083</v>
+        <v>0.1235951483249664</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.02045406214892864</v>
+        <v>0.1127772703766823</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04896673932671547</v>
+        <v>0.1277899444103241</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.02905838191509247</v>
+        <v>0.0429098829627037</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.02163996547460556</v>
+        <v>0.004431706853210926</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.03138886392116547</v>
+        <v>0.06683151423931122</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.006208615377545357</v>
+        <v>0.009493058547377586</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.03229715675115585</v>
+        <v>0.276326984167099</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.05452577397227287</v>
+        <v>0.05179070308804512</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.04910299554467201</v>
+        <v>0.2310446202754974</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.004939310252666473</v>
+        <v>0.0899406224489212</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.04468736425042152</v>
+        <v>0.1935701072216034</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0335359163582325</v>
+        <v>0.09678556770086288</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0377482958137989</v>
+        <v>0.1673164218664169</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.03272994980216026</v>
+        <v>0.1053221076726913</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.013138797134161</v>
+        <v>0.3450318574905396</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.08496060967445374</v>
+        <v>0.5344736576080322</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.02928194962441921</v>
+        <v>0.06301936507225037</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.09293189644813538</v>
+        <v>0.2954095005989075</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.06183003261685371</v>
+        <v>0.07244390249252319</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.009614067152142525</v>
+        <v>0.1052301675081253</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.02452370524406433</v>
+        <v>0.2145692408084869</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.01668340899050236</v>
+        <v>0.002361994236707687</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.003766804933547974</v>
+        <v>0.0776345357298851</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.07583771646022797</v>
+        <v>0.1282779425382614</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01706644706428051</v>
+        <v>0.07543957978487015</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.01780634000897408</v>
+        <v>0.07154873013496399</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.005877618212252855</v>
+        <v>0.199202686548233</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.03433831781148911</v>
+        <v>0.03074577450752258</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.02571260929107666</v>
+        <v>0.08077049255371094</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.2002549916505814</v>
+        <v>0.0911688506603241</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.01086142845451832</v>
+        <v>0.01450487971305847</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.03880258277058601</v>
+        <v>0.09038956463336945</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.007932856678962708</v>
+        <v>0.0001889964478323236</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02577734924852848</v>
+        <v>0.001373329083435237</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001470871036872268</v>
+        <v>0.0001225907617481425</v>
       </c>
       <c r="D10" t="n">
-        <v>0.007322455756366253</v>
+        <v>0.0005942573770880699</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008332409895956516</v>
+        <v>0.0004476147005334496</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0006805340526625514</v>
+        <v>0.0004307707422412932</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002283164067193866</v>
+        <v>0.0003349188482388854</v>
       </c>
       <c r="H10" t="n">
-        <v>0.003207980189472437</v>
+        <v>0.0006139424513094127</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001277273637242615</v>
+        <v>0.0002269883552799001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.006206990219652653</v>
+        <v>5.128614066052251e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01925135217607021</v>
+        <v>0.001577587332576513</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002340571023523808</v>
+        <v>3.607999315136112e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01364952325820923</v>
+        <v>0.001105901203118265</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01271630730479956</v>
+        <v>0.001120476867072284</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004703526385128498</v>
+        <v>0.0004953816533088684</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003797572338953614</v>
+        <v>0.0002320668136235327</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01583203859627247</v>
+        <v>0.0001643849827814847</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00161421368829906</v>
+        <v>0.0001361093600280583</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0007204997236840427</v>
+        <v>0.0001027937032631598</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01153465453535318</v>
+        <v>0.0004217858368065208</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0001905073731904849</v>
+        <v>0.0001171284529846162</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0002753563458099961</v>
+        <v>0.0004001360211987048</v>
       </c>
       <c r="W10" t="n">
-        <v>0.005711445584893227</v>
+        <v>0.0003730400349013507</v>
       </c>
       <c r="X10" t="n">
-        <v>0.003740556072443724</v>
+        <v>0.0001061578223016113</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.004067912232130766</v>
+        <v>9.336785296909511e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.001476195175200701</v>
+        <v>3.429556818446144e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001991151599213481</v>
+        <v>0.0001199097823700868</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.005118688568472862</v>
+        <v>3.184708475600928e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.007026046048849821</v>
+        <v>5.541866994462907e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.004489159677177668</v>
+        <v>0.0001842839119490236</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.006615094840526581</v>
+        <v>0.0006271933089010417</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.004758074879646301</v>
+        <v>0.0008833850733935833</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0004306462360545993</v>
+        <v>3.333843778818846e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.006812247447669506</v>
+        <v>4.239496047375724e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.003472653916105628</v>
+        <v>0.0004662582650780678</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0006734210764989257</v>
+        <v>0.0001084723262465559</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.005126910284161568</v>
+        <v>1.462417640141211e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.006912511773407459</v>
+        <v>0.0005241640610620379</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0005705206422135234</v>
+        <v>3.002601624757517e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001576295355334878</v>
+        <v>9.874180250335485e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0003769909671973437</v>
+        <v>7.726522744633257e-05</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.001406802679412067</v>
+        <v>4.910682037007064e-05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.002278969157487154</v>
+        <v>9.434944513486698e-05</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0007326493505388498</v>
+        <v>0.0002039852552115917</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.001859343028627336</v>
+        <v>0.0001176353398477659</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.00877761747688055</v>
+        <v>0.0001970373268704861</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.02751647494733334</v>
+        <v>0.00180889293551445</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.004898596554994583</v>
+        <v>1.519079523859546e-05</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.00130978471133858</v>
+        <v>0.0001073372768587433</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.003305660560727119</v>
+        <v>0.001123296096920967</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.243863703683019e-06</v>
+        <v>0.0001900423230836168</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001004039775580168</v>
+        <v>8.430533489445224e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.005613801535218954</v>
+        <v>2.196201603510417e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0003140599001199007</v>
+        <v>0.0001975787454284728</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.004246861208230257</v>
+        <v>0.0003053033724427223</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.003308265237137675</v>
+        <v>0.0004467629187274724</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.00428247032687068</v>
+        <v>8.555261592846364e-05</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.004552064463496208</v>
+        <v>0.0004005293303634971</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.007454440463334322</v>
+        <v>0.0003982784401159734</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.003582568140700459</v>
+        <v>4.763976539834403e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0009401781135238707</v>
+        <v>8.000865636859089e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01105805207043886</v>
+        <v>0.000313393771648407</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0002281744382344186</v>
+        <v>0.0001070076104952022</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.002501898212358356</v>
+        <v>0.0001389211683999747</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.007447283249348402</v>
+        <v>0.0003089608217123896</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.002036649035289884</v>
+        <v>0.0001062996889231727</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.01051430683583021</v>
+        <v>7.014203583821654e-05</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0114483255892992</v>
+        <v>0.0001867313403636217</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.005667570978403091</v>
+        <v>0.0001427107927156612</v>
       </c>
       <c r="BR10" t="n">
-        <v>1.738924765959382e-05</v>
+        <v>0.0005383069510571659</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.004685454536229372</v>
+        <v>0.0002221681061200798</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.00163604982662946</v>
+        <v>1.168131348094903e-05</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.004292059689760208</v>
+        <v>0.0003209324786439538</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.01503995060920715</v>
+        <v>0.001212552189826965</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.002268335316330194</v>
+        <v>3.599964111344889e-05</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.001376911881379783</v>
+        <v>0.0004388624802231789</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.001181753119453788</v>
+        <v>0.000471506966277957</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.001969607314094901</v>
+        <v>0.000182047559064813</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.007120163645595312</v>
+        <v>0.0003269091248512268</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003783403895795345</v>
+        <v>3.774823562707752e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.00110485078766942</v>
+        <v>5.002406032872386e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0009022966842167079</v>
+        <v>1.432546469004592e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.004510359838604927</v>
+        <v>0.0003785279404837638</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0001840753830038011</v>
+        <v>0.0001012206630548462</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.004092113114893436</v>
+        <v>4.843368515139446e-05</v>
       </c>
       <c r="CH10" t="n">
-        <v>9.881430014502257e-05</v>
+        <v>0.0001892009167931974</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001472388627007604</v>
+        <v>0.0001402369525749236</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0004223590367473662</v>
+        <v>9.047106868820265e-05</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0001842819037847221</v>
+        <v>9.083735494641587e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.001545175211504102</v>
+        <v>2.814920298988e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01206103898584843</v>
+        <v>0.0003035150002688169</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01088284980505705</v>
+        <v>0.0007147113210521638</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0004353885306045413</v>
+        <v>0.000108339219877962</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.004951523151248693</v>
+        <v>0.0005392280872911215</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.01303276978433132</v>
+        <v>0.001085717114619911</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.001342760515399277</v>
+        <v>0.0001559668889967725</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.001757932361215353</v>
+        <v>0.0002467544982209802</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.001627929857932031</v>
+        <v>0.0001721123699098825</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0002998257405124605</v>
+        <v>3.381260466994718e-05</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0001009054249152541</v>
+        <v>9.528260852675885e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.004017917905002832</v>
+        <v>0.0003572294663172215</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0009038745192810893</v>
+        <v>9.652044536778703e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.005718246567994356</v>
+        <v>9.372615750180557e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0002556472318246961</v>
+        <v>0.0001624573196750134</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.002081054961308837</v>
+        <v>0.0001382500631734729</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0004411252157296985</v>
+        <v>5.655800850945525e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.001661871327087283</v>
+        <v>1.153818357124692e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.00109944143332541</v>
+        <v>3.45551670761779e-05</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.01083397772163153</v>
+        <v>0.0004818119050469249</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.01990207470953465</v>
+        <v>0.00010894348815782</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.002876560436561704</v>
+        <v>9.61752375587821e-05</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01008364278823137</v>
+        <v>0.0001153969060396776</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001998697174713016</v>
+        <v>0.000203377625439316</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.002698839642107487</v>
+        <v>0.0001028510159812868</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01493408810347319</v>
+        <v>6.872232188470662e-05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.003031140426173806</v>
+        <v>9.290194429922849e-05</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0003526093496475369</v>
+        <v>0.0003938830923289061</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.005720242392271757</v>
+        <v>9.269226575270295e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.006563286297023296</v>
+        <v>0.0002425165002932772</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.001634565182030201</v>
+        <v>2.62135890807258e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0004940323997288942</v>
+        <v>0.0003360496484674513</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.005637760274112225</v>
+        <v>0.0001534178445581347</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.002074817661195993</v>
+        <v>0.0002530865895096213</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.004521906841546297</v>
+        <v>0.0001816045114537701</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.0003561359189916402</v>
+        <v>0.0002158803399652243</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.003185298526659608</v>
+        <v>3.194064629497007e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.001529667293652892</v>
+        <v>0.000152584194438532</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0002881675027310848</v>
+        <v>0.0003379747795406729</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.002798715606331825</v>
+        <v>0.0001352446270175278</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.00539806392043829</v>
+        <v>0.0001128990188590251</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.004997302312403917</v>
+        <v>0.000557763734832406</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0006965588545426726</v>
+        <v>2.094297087751329e-05</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.003256865544244647</v>
+        <v>0.0002678845485206693</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.001685741008259356</v>
+        <v>1.562169200042263e-05</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.001734242308884859</v>
+        <v>0.000103478116216138</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.003531458554789424</v>
+        <v>9.288766159443185e-05</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.002618097700178623</v>
+        <v>6.951465911697596e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.0003768842434510589</v>
+        <v>5.835532647324726e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.01025423873215914</v>
+        <v>0.0001172333650174551</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.002551381243392825</v>
+        <v>0.0001354892156086862</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.002017690800130367</v>
+        <v>0.0001336758577963337</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.001786037115380168</v>
+        <v>3.160299092996866e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.00174108671490103</v>
+        <v>3.273444599471986e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0005650732200592756</v>
+        <v>5.032828630646691e-05</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.002693346701562405</v>
+        <v>0.0001171623007394373</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0004723543825093657</v>
+        <v>0.0001425880182068795</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.003974697086960077</v>
+        <v>2.569120988482609e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.003432042431086302</v>
+        <v>3.975217987317592e-05</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.002032083459198475</v>
+        <v>0.0002127856569131836</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.002992274006828666</v>
+        <v>0.0001329065562458709</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001049506361596286</v>
+        <v>5.177575076231733e-05</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.002699804725125432</v>
+        <v>3.529681634972803e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.001255988259799778</v>
+        <v>0.0002054879732895643</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0006759213865734637</v>
+        <v>1.353241168544628e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.003082334762439132</v>
+        <v>0.0004185365105513483</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.000377671851310879</v>
+        <v>6.309723539743572e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.003919463604688644</v>
+        <v>7.781513704685494e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0009960496099665761</v>
+        <v>0.0001341723254881799</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001800822443328798</v>
+        <v>0.000140697171445936</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.00120525062084198</v>
+        <v>8.286535739898682e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0007431705016642809</v>
+        <v>1.32565355670522e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0009916946291923523</v>
+        <v>4.396815347718075e-05</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.004816002678126097</v>
+        <v>0.0001376696745865047</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.005432236939668655</v>
+        <v>0.0001177754093077965</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.002766958903521299</v>
+        <v>2.780110480671283e-05</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.002417886396870017</v>
+        <v>0.0002226318320026621</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.001780584105290473</v>
+        <v>0.0002899476094171405</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.001869285013526678</v>
+        <v>4.6724577259738e-05</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.001735456986352801</v>
+        <v>7.722473674220964e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>2.085580490529537e-06</v>
+        <v>0.0003838174743577838</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0004801842151209712</v>
+        <v>4.288338095648214e-05</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0001941947266459465</v>
+        <v>0.0001275576214538887</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.001779906218871474</v>
+        <v>0.0004213950887788087</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.002222888404503465</v>
+        <v>0.0001424186630174518</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.009526392444968224</v>
+        <v>0.0002490140032023191</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.005897046532481909</v>
+        <v>0.0008075855439528823</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0005723538342863321</v>
+        <v>0.0002069890033453703</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.001529734116047621</v>
+        <v>0.0001558966469019651</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.007425857242196798</v>
+        <v>2.301485073985532e-05</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.001273832516744733</v>
+        <v>0.0001453646400477737</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0005674734711647034</v>
+        <v>0.0001818730670493096</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.008964279666543007</v>
+        <v>0.0002194318803958595</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.004055289085954428</v>
+        <v>0.0002897125959862024</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.007717376109212637</v>
+        <v>0.0001127588475355878</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.005527990870177746</v>
+        <v>0.0001986010611290112</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.004829930607229471</v>
+        <v>0.0001391272526234388</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.007299049757421017</v>
+        <v>0.0001609119208296761</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.009782526642084122</v>
+        <v>0.000148240098496899</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.001857413444668055</v>
+        <v>0.0001774398551788181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03468569368124008</v>
+        <v>0.008006015792489052</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2304315268993378</v>
+        <v>0.01110736280679703</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00364498351700604</v>
+        <v>0.001940371003001928</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06026255711913109</v>
+        <v>0.0003589216503314674</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04774196445941925</v>
+        <v>0.003875309135764837</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04817932471632957</v>
+        <v>0.0009818242397159338</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0202962476760149</v>
+        <v>0.00174996757414192</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03068861365318298</v>
+        <v>0.0023314009886235</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03728534653782845</v>
+        <v>0.002440053969621658</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04057872667908669</v>
+        <v>0.007886775769293308</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1786040067672729</v>
+        <v>0.01599990762770176</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002172365318983793</v>
+        <v>0.002556228544563055</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05011249333620071</v>
+        <v>0.002474985551089048</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06938368827104568</v>
+        <v>0.005568984895944595</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05045506358146667</v>
+        <v>0.002017670776695013</v>
       </c>
       <c r="P11" t="n">
-        <v>0.009835397824645042</v>
+        <v>0.0007749747601337731</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02712742425501347</v>
+        <v>0.0005155879771336913</v>
       </c>
       <c r="R11" t="n">
-        <v>0.04998242482542992</v>
+        <v>0.004949566442519426</v>
       </c>
       <c r="S11" t="n">
-        <v>0.008924354799091816</v>
+        <v>0.0008616556879132986</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04780682548880577</v>
+        <v>0.0006380168488249183</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004263845272362232</v>
+        <v>0.0006173576111905277</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02170123532414436</v>
+        <v>0.001197376754134893</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03910066187381744</v>
+        <v>0.0001987205323530361</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03534236550331116</v>
+        <v>0.0008439809316769242</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.02519400045275688</v>
+        <v>4.695894313044846e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.03784313797950745</v>
+        <v>0.002321140142157674</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02310406789183617</v>
+        <v>0.002319689840078354</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01263311319053173</v>
+        <v>0.000805241463240236</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.007963970303535461</v>
+        <v>0.001446066307835281</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001769413240253925</v>
+        <v>0.0006437008269131184</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.004344046115875244</v>
+        <v>0.001476920442655683</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02742171473801136</v>
+        <v>0.002326664049178362</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.05497945845127106</v>
+        <v>0.000701769080478698</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.01578608341515064</v>
+        <v>0.0008572824881412089</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.00348326563835144</v>
+        <v>0.00106109376065433</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01374913286417723</v>
+        <v>0.0002099229022860527</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.03736318647861481</v>
+        <v>0.0010510009014979</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.05462007224559784</v>
+        <v>0.00333414925262332</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.01449438091367483</v>
+        <v>0.002161439275369048</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.004713802132755518</v>
+        <v>0.001658760593272746</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.003484823042526841</v>
+        <v>7.98502005636692e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.02530515566468239</v>
+        <v>0.0005311972927302122</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0008932310156524181</v>
+        <v>0.001172696705907583</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.01344011817127466</v>
+        <v>0.001227857079356909</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.01256027445197105</v>
+        <v>0.0003971746773459017</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.004190332721918821</v>
+        <v>0.002736733527854085</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1513236612081528</v>
+        <v>0.009046850726008415</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.001402716268785298</v>
+        <v>0.001167976530268788</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.01182623021304607</v>
+        <v>0.00153995759319514</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.006365088745951653</v>
+        <v>0.003336584893986583</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.02572965994477272</v>
+        <v>0.00126419635489583</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.001824995502829552</v>
+        <v>0.0001499317440902814</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.002652611350640655</v>
+        <v>1.705833710730076e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.975132808089256e-06</v>
+        <v>0.0007835680153220892</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0035701934248209</v>
+        <v>0.002155901398509741</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02261505834758282</v>
+        <v>9.433925151824951e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.001495747361332178</v>
+        <v>0.002285043941810727</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.01188762206584215</v>
+        <v>0.0002264055074192584</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.04915806651115417</v>
+        <v>0.002234685467556119</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.004128099419176579</v>
+        <v>0.003197430167347193</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.01345061045140028</v>
+        <v>0.0004793669795617461</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.007736751809716225</v>
+        <v>2.03945382963866e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.03418122231960297</v>
+        <v>0.002179335569962859</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01163980644196272</v>
+        <v>0.0006758458912372589</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0147472508251667</v>
+        <v>0.001442067441530526</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.01155652943998575</v>
+        <v>0.0004419185570441186</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0002859283704310656</v>
+        <v>0.0003356517117936164</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01680160313844681</v>
+        <v>0.002302843844518065</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01768122054636478</v>
+        <v>0.0004090961592737585</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01103659812361002</v>
+        <v>0.002968205371871591</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.01610415056347847</v>
+        <v>0.0002777219633571804</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.02231390401721001</v>
+        <v>0.0002283768553752452</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.01994093507528305</v>
+        <v>0.0007667045574635267</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1183612868189812</v>
+        <v>0.006445247679948807</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.01082479674369097</v>
+        <v>0.0007532695890404284</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.04578834399580956</v>
+        <v>0.001777882338501513</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01758826710283756</v>
+        <v>0.001089004217647016</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.002566629089415073</v>
+        <v>0.000172093088622205</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.01614568941295147</v>
+        <v>0.001700295368209481</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.01839510537683964</v>
+        <v>0.0005250924732536077</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.02110292948782444</v>
+        <v>0.001995394006371498</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.01410489343106747</v>
+        <v>0.00238650874234736</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.02617056109011173</v>
+        <v>0.003835190553218126</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.00762628298252821</v>
+        <v>0.0002614175900816917</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.012996188364923</v>
+        <v>4.829780664294958e-06</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.006168273743242025</v>
+        <v>2.12757040571887e-05</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.00770215317606926</v>
+        <v>0.00110618444159627</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.009568950161337852</v>
+        <v>0.0008358526392839849</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.005403670482337475</v>
+        <v>0.0001485381071688607</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.006062959786504507</v>
+        <v>0.0004214947111904621</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.03959646821022034</v>
+        <v>0.0008425746345892549</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.002744609955698252</v>
+        <v>0.006808820180594921</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0004275833780411631</v>
+        <v>0.0004197283124085516</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.01170823723077774</v>
+        <v>0.002244484378024936</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.05990557372570038</v>
+        <v>0.0002879470121115446</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.01138416957110167</v>
+        <v>0.002727440791204572</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0387931764125824</v>
+        <v>0.001523443264886737</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.03099732287228107</v>
+        <v>0.001916332286782563</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.005299638025462627</v>
+        <v>0.001484307926148176</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.007516337092965841</v>
+        <v>0.002125483704730868</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.03214424476027489</v>
+        <v>0.003653163556009531</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.007475089281797409</v>
+        <v>2.782227238640189e-05</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0165505763143301</v>
+        <v>0.0003999383188784122</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.004666280932724476</v>
+        <v>0.0004324683977756649</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02113377302885056</v>
+        <v>0.0009039197466336191</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01127643510699272</v>
+        <v>0.0005308460094965994</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.009514014236629009</v>
+        <v>0.0001933830353664234</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.001812099479138851</v>
+        <v>0.0008300244808197021</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.001394676859490573</v>
+        <v>0.001676807412877679</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.06104137003421783</v>
+        <v>0.004099702462553978</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.01417741365730762</v>
+        <v>0.0001648152829147875</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.06483285129070282</v>
+        <v>0.0007462233770638704</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01892015337944031</v>
+        <v>0.00295954872854054</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.04790213704109192</v>
+        <v>0.003551253350451589</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.001551270484924316</v>
+        <v>0.0008921884000301361</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.004854658618569374</v>
+        <v>0.0002959882258437574</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.02450384944677353</v>
+        <v>0.003152728779241443</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.01344948727637529</v>
+        <v>0.00133996712975204</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.02116064913570881</v>
+        <v>0.001956557622179389</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.008942476473748684</v>
+        <v>0.001900083851069212</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.02141338214278221</v>
+        <v>0.0005174846737645566</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01565233059227467</v>
+        <v>0.0005058983224444091</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.00296326307579875</v>
+        <v>0.001968977507203817</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0133869843557477</v>
+        <v>0.000848735508043319</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.005855904426425695</v>
+        <v>0.002680488163605332</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.03018786385655403</v>
+        <v>0.0006661844090558589</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.005451527889817953</v>
+        <v>0.001176665769889951</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0148030836135149</v>
+        <v>0.001813388895243406</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.02727090194821358</v>
+        <v>0.001428293995559216</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.005714026279747486</v>
+        <v>0.001824026578105986</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01899673230946064</v>
+        <v>0.002034489763900638</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.005682737100869417</v>
+        <v>0.00406219344586134</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.005191062111407518</v>
+        <v>0.001504822284914553</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.004712437279522419</v>
+        <v>0.002389820292592049</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.01206409372389317</v>
+        <v>0.001785670057870448</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.004443877376616001</v>
+        <v>0.001941676950082183</v>
       </c>
       <c r="EG11" t="n">
-        <v>1.974584301933646e-05</v>
+        <v>0.0009717820212244987</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.007526720874011517</v>
+        <v>0.0008744286024011672</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.002811377868056297</v>
+        <v>2.734735608100891e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01081440132111311</v>
+        <v>0.0009652719018049538</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.02565654739737511</v>
+        <v>0.00116208428516984</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.00438335444778204</v>
+        <v>0.0004240748821757734</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.002099090721458197</v>
+        <v>0.0005461912951432168</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.002107417210936546</v>
+        <v>0.0002030143805313855</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.01484781689941883</v>
+        <v>0.000876748061273247</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.006807435769587755</v>
+        <v>0.002116551157087088</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.001906551420688629</v>
+        <v>0.001216511474922299</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.001093707513064146</v>
+        <v>0.001618930837139487</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01476447004824877</v>
+        <v>2.843660149665084e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.04872629791498184</v>
+        <v>0.001282936776988208</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.02413319982588291</v>
+        <v>0.0004969488945789635</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.04778793081641197</v>
+        <v>0.0004392644623294473</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0113488519564271</v>
+        <v>0.002648116089403629</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.00955900177359581</v>
+        <v>0.002381507074460387</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.03034671023488045</v>
+        <v>0.004483827389776707</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.002737225731834769</v>
+        <v>0.0003596734022721648</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.01774978637695312</v>
+        <v>0.0002142044831998646</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01149822305887938</v>
+        <v>0.0004096672055311501</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0122890817001462</v>
+        <v>0.0008845140691846609</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.01646220684051514</v>
+        <v>0.0005982014117762446</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0008034716593101621</v>
+        <v>0.0002762195363175124</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0071293362416327</v>
+        <v>0.0009738229564391077</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.003072794061154127</v>
+        <v>0.0008140611462295055</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.02968758158385754</v>
+        <v>0.00259618298150599</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.009567605331540108</v>
+        <v>0.001672523794695735</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.02541985735297203</v>
+        <v>0.001454123528674245</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.001034821500070393</v>
+        <v>0.001502031343989074</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01412237901240587</v>
+        <v>4.329631337895989e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.009368119761347771</v>
+        <v>0.001569977961480618</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.02016894146800041</v>
+        <v>0.001751851057633758</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.006761663593351841</v>
+        <v>0.003051445819437504</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.002753428416326642</v>
+        <v>8.432008326053619e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.07008940726518631</v>
+        <v>0.0001474475720897317</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.01325458195060492</v>
+        <v>0.002351046074181795</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.05652591586112976</v>
+        <v>0.001216263743117452</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02731721475720406</v>
+        <v>0.003554613096639514</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.009592863731086254</v>
+        <v>0.0005245498032309115</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.03574923425912857</v>
+        <v>0.002219460438936949</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.01895685866475105</v>
+        <v>0.003986563999205828</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.003193545155227184</v>
+        <v>0.0009054497932083905</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.01717414148151875</v>
+        <v>0.001733271987177432</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.005347234662622213</v>
+        <v>0.0003754240460693836</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.002702792640775442</v>
+        <v>0.0008582183509133756</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.006324952468276024</v>
+        <v>0.002497857436537743</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.1022794395685196</v>
+        <v>0.0004914533928968012</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.02015914209187031</v>
+        <v>8.143828017637134e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.09820006787776947</v>
+        <v>0.0001504436513641849</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.01102563086897135</v>
+        <v>0.002093299757689238</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.01426885556429625</v>
+        <v>0.00384236266836524</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.01013845764100552</v>
+        <v>0.0001699722779449075</v>
       </c>
       <c r="B12" t="n">
-        <v>0.04491573572158813</v>
+        <v>0.001680768793448806</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004828461911529303</v>
+        <v>0.0002903032873291522</v>
       </c>
       <c r="D12" t="n">
-        <v>0.007792601361870766</v>
+        <v>0.0005572540685534477</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01292853616178036</v>
+        <v>0.0009183216607198119</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00445549888536334</v>
+        <v>0.0005078801768831909</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02124584093689919</v>
+        <v>0.0006753115449100733</v>
       </c>
       <c r="H12" t="n">
-        <v>0.002968453336507082</v>
+        <v>0.0001857020251918584</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00115259422454983</v>
+        <v>0.0005061937845312059</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01218260452151299</v>
+        <v>0.0001746272610034794</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03182101994752884</v>
+        <v>0.002265512477606535</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003975523170083761</v>
+        <v>0.0001746000489220023</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01893038302659988</v>
+        <v>0.0007517370395362377</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01806020177900791</v>
+        <v>0.0008312118006870151</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01056493073701859</v>
+        <v>0.0001536590571049601</v>
       </c>
       <c r="P12" t="n">
-        <v>0.02052716724574566</v>
+        <v>0.0009042754536494613</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01487406808882952</v>
+        <v>0.0003121765330433846</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001206580665893853</v>
+        <v>0.0003345375589560717</v>
       </c>
       <c r="S12" t="n">
-        <v>0.002760231029242277</v>
+        <v>7.186338189058006e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01444163080304861</v>
+        <v>5.159355714567937e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.004669232293963432</v>
+        <v>0.0001779049052856863</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001202794373966753</v>
+        <v>9.351626067655161e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01193823665380478</v>
+        <v>0.0002909371687564999</v>
       </c>
       <c r="X12" t="n">
-        <v>0.006501834373921156</v>
+        <v>0.0002675213327165693</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0007627367740496993</v>
+        <v>0.0001336631685262546</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0008920172112993896</v>
+        <v>3.131609264528379e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.005025433842092752</v>
+        <v>0.0001516532356617972</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.003744017798453569</v>
+        <v>0.0001550388697069138</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01061399467289448</v>
+        <v>0.0001765643828548491</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.003827516920864582</v>
+        <v>0.0004393409180920571</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.005067658610641956</v>
+        <v>0.0001488645939389244</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.006035967264324427</v>
+        <v>0.0001969454460777342</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.001322427531704307</v>
+        <v>0.0001281485601793975</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.00407470902428031</v>
+        <v>0.0001410540862707421</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.001788950874470174</v>
+        <v>0.0001229359913850203</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.00292293424718082</v>
+        <v>0.0001572768378537148</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.009264509193599224</v>
+        <v>2.397586467850488e-05</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.00845333281904459</v>
+        <v>0.0005078286048956215</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0006812301580794156</v>
+        <v>0.0001251556095667183</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.004027975257486105</v>
+        <v>3.330212712171488e-05</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.001093321130611002</v>
+        <v>0.0002468384336680174</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0005429822485893965</v>
+        <v>0.0002204052434535697</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.004832725040614605</v>
+        <v>4.97151049785316e-05</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.00398799916729331</v>
+        <v>0.0001481666113249958</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.003683775430545211</v>
+        <v>1.343715121038258e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.01032352447509766</v>
+        <v>8.257293666247278e-05</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.04392963647842407</v>
+        <v>0.001545371720567346</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.003445244859904051</v>
+        <v>0.0003011421067640185</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.009557786397635937</v>
+        <v>8.005095878615975e-05</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.008529610000550747</v>
+        <v>0.0003052719112019986</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.005186780821532011</v>
+        <v>0.0002201930910814553</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.005871804896742105</v>
+        <v>9.538209269521758e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.009976409375667572</v>
+        <v>0.0005603248719125986</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.003338404465466738</v>
+        <v>9.275940828956664e-05</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.007508560549467802</v>
+        <v>2.523933653719723e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.005113799124956131</v>
+        <v>0.0002557221741881222</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.01080427784472704</v>
+        <v>0.0002909784961957484</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.002171321772038937</v>
+        <v>0.0001893133739940822</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01790737174451351</v>
+        <v>0.000503526593092829</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0005207374924793839</v>
+        <v>0.000444234989117831</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.009214025922119617</v>
+        <v>0.0001900300267152488</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.01291374117136002</v>
+        <v>0.0001777837751433253</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.003754380159080029</v>
+        <v>0.0002455678186379373</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0005321080097928643</v>
+        <v>0.000119988588267006</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01061334647238255</v>
+        <v>0.000196217413758859</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.002454777946695685</v>
+        <v>5.349257116904482e-05</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01584034785628319</v>
+        <v>0.0002893528726417571</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01867745257914066</v>
+        <v>0.0005399027140811086</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.003118916880339384</v>
+        <v>0.0001699525600997731</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.005002615507692099</v>
+        <v>0.0001619659597054124</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.008765451610088348</v>
+        <v>0.0001325126504525542</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.001961428439244628</v>
+        <v>0.000338356418069452</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.003327514044940472</v>
+        <v>0.0002018109080381691</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0201238077133894</v>
+        <v>0.0008854378829710186</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.00736425444483757</v>
+        <v>1.200219412567094e-05</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0038900061044842</v>
+        <v>0.0001994530903175473</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0009307037107646465</v>
+        <v>0.000289249699562788</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0001101544403354637</v>
+        <v>0.0002271060075145215</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.004528291989117861</v>
+        <v>2.738826879067346e-06</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.007961783558130264</v>
+        <v>0.0003119319153483957</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.00239044614136219</v>
+        <v>0.0001750393857946619</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0009661887306720018</v>
+        <v>2.637454053910915e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.009080036543309689</v>
+        <v>0.0005624846089631319</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.003783015068620443</v>
+        <v>4.016534876427613e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.004816869739443064</v>
+        <v>0.0001981188252102584</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.000849310599733144</v>
+        <v>0.0001511235896032304</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.001534913550131023</v>
+        <v>0.0002142639132216573</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.003828268265351653</v>
+        <v>0.0001302963064517826</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0008959355764091015</v>
+        <v>6.40234793536365e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.002737559843808413</v>
+        <v>0.000249382050242275</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.01653129048645496</v>
+        <v>5.329059058567509e-05</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.01475517544895411</v>
+        <v>0.0009812393691390753</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0009821975836530328</v>
+        <v>1.307434285990894e-05</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.005925466306507587</v>
+        <v>1.115812483476475e-05</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01482556201517582</v>
+        <v>6.380008562700823e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>8.820340735837817e-05</v>
+        <v>0.0003861756413243711</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.003564458806067705</v>
+        <v>0.0003199698985554278</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.002002615015953779</v>
+        <v>7.702337461523712e-05</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0004397220036480576</v>
+        <v>4.799127054866403e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.002235643099993467</v>
+        <v>2.467445483489428e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.007877793163061142</v>
+        <v>0.0005973809747956693</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.004117077216506004</v>
+        <v>4.019129846710712e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.00801919586956501</v>
+        <v>0.000132413551909849</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.001428337534889579</v>
+        <v>0.0001146153517765924</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.001789203146472573</v>
+        <v>0.0002018977247644216</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.00510248402133584</v>
+        <v>0.0001512934832135215</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.001080669229850173</v>
+        <v>0.0001142916953540407</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.00222674710676074</v>
+        <v>0.000296350714052096</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.01082323491573334</v>
+        <v>0.000129552063299343</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.02046989649534225</v>
+        <v>8.643846376799047e-05</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.003092572558671236</v>
+        <v>0.0004229412297718227</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01291760616004467</v>
+        <v>3.769737668335438e-05</v>
       </c>
       <c r="DI12" t="n">
-        <v>8.984701707959175e-06</v>
+        <v>0.0001654493098612875</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.002049885224550962</v>
+        <v>8.201336459023878e-05</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.01206556148827076</v>
+        <v>6.999609468039125e-06</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.004854641854763031</v>
+        <v>0.0004242233990225941</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.005178837105631828</v>
+        <v>4.218577669234946e-05</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.002800597110763192</v>
+        <v>9.309862070949748e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.003887638915330172</v>
+        <v>0.0001841209013946354</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.004344974178820848</v>
+        <v>0.0001042503718053922</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.002059477381408215</v>
+        <v>0.0003220067301299423</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.00180246657691896</v>
+        <v>0.0001237671676790342</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.003133918158710003</v>
+        <v>0.0004450756532605737</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.00224382895976305</v>
+        <v>0.0003674954350572079</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.003618279937654734</v>
+        <v>0.0001098061329685152</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.005678418092429638</v>
+        <v>0.0004897278849966824</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.001514633186161518</v>
+        <v>0.0001999349624384195</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.003008423605933785</v>
+        <v>0.0003924152697436512</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.006243413314223289</v>
+        <v>5.400417285272852e-05</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.009099687449634075</v>
+        <v>0.0003654728934634477</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.006025618873536587</v>
+        <v>0.0002120422141160816</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.005088955163955688</v>
+        <v>0.000559131964109838</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.002795018255710602</v>
+        <v>0.0001430215343134478</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.000720833835657686</v>
+        <v>0.0003360181290190667</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.001761699561029673</v>
+        <v>0.0002251140540465713</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.00591711001470685</v>
+        <v>2.903249333030544e-05</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0004284465103410184</v>
+        <v>0.0006281389505602419</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.001672312617301941</v>
+        <v>0.0001269871718250215</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01024593971669674</v>
+        <v>2.99663697660435e-05</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.0007315700058825314</v>
+        <v>0.0001427507086191326</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.00227897334843874</v>
+        <v>0.0001996581995626912</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.005718585103750229</v>
+        <v>3.964788265875541e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.00189788278657943</v>
+        <v>4.165129212196916e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0008525619050487876</v>
+        <v>0.0002505276934243739</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.007104464806616306</v>
+        <v>4.895831807516515e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.002722292440012097</v>
+        <v>0.0003007379127666354</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.006077069323509932</v>
+        <v>7.821968756616116e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.00575184216722846</v>
+        <v>0.0002484371070750058</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.004597282502800226</v>
+        <v>0.0001034383458318189</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001775983022525907</v>
+        <v>3.718843800015748e-05</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.004597592633217573</v>
+        <v>2.683184357010759e-05</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.003948372788727283</v>
+        <v>0.0001378088491037488</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.002769257640466094</v>
+        <v>0.0001089648794732057</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.001936646527610719</v>
+        <v>1.706262628431432e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.007235286757349968</v>
+        <v>0.0006715235067531466</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.002467634622007608</v>
+        <v>4.443663056008518e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.005464702844619751</v>
+        <v>0.0001249392225872725</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.00207722932100296</v>
+        <v>8.028007869143039e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.00161929230671376</v>
+        <v>0.0001873112050816417</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.005490787792950869</v>
+        <v>0.0001134918275056407</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.001856385730206966</v>
+        <v>8.755983435548842e-05</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.00309819052927196</v>
+        <v>0.0002849031880032271</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.006573956925421953</v>
+        <v>0.0003688264405354857</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.009398838505148888</v>
+        <v>0.000145530968438834</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.007175484672188759</v>
+        <v>0.000304313056403771</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.003671058919280767</v>
+        <v>0.0001608612365089357</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.004459508694708347</v>
+        <v>1.625240292923991e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.001311143976636231</v>
+        <v>0.0005104562733322382</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0007546539418399334</v>
+        <v>5.116355896461755e-05</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.002195666776970029</v>
+        <v>0.0004465348029043525</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.005531944334506989</v>
+        <v>0.0006408903864212334</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.006817142013460398</v>
+        <v>0.000297726335702464</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.0046324054710567</v>
+        <v>0.0008766576065681875</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.001880104653537273</v>
+        <v>0.0002183459582738578</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01505956426262856</v>
+        <v>0.0005262487684376538</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01407877914607525</v>
+        <v>0.0001705695322016254</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.006088698748499155</v>
+        <v>0.0006224998505786061</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.005059945862740278</v>
+        <v>0.0002766043180599809</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.005836235359311104</v>
+        <v>0.0004554368206299841</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.002383790910243988</v>
+        <v>0.0003800230042543262</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.009420793503522873</v>
+        <v>1.454894299968146e-05</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.008539561182260513</v>
+        <v>0.0004891337594017386</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0002502181159798056</v>
+        <v>0.0002874530619010329</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.01019492466002703</v>
+        <v>0.0001623120333533734</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.003279958385974169</v>
+        <v>0.0008563241572119296</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.004470141604542732</v>
+        <v>0.0001550349406898022</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0111958822235465</v>
+        <v>6.854883395135403e-05</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.01192291546612978</v>
+        <v>0.0001210776681546122</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.002873700577765703</v>
+        <v>8.431203605141491e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01998426206409931</v>
+        <v>0.1237598806619644</v>
       </c>
       <c r="B13" t="n">
-        <v>0.07634875178337097</v>
+        <v>0.2645007967948914</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01036971528083086</v>
+        <v>0.099777452647686</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01105710491538048</v>
+        <v>0.1162022799253464</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01911376416683197</v>
+        <v>0.09233587980270386</v>
       </c>
       <c r="F13" t="n">
-        <v>0.007541230414062738</v>
+        <v>0.2501453459262848</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01134688965976238</v>
+        <v>0.03886980935931206</v>
       </c>
       <c r="H13" t="n">
-        <v>0.005827587563544512</v>
+        <v>0.1201053783297539</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04416980594396591</v>
+        <v>0.1735983192920685</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02403829246759415</v>
+        <v>0.05710393935441971</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06003542989492416</v>
+        <v>0.3447893261909485</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01165700331330299</v>
+        <v>0.09365002810955048</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01765034161508083</v>
+        <v>0.0307116936892271</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02669822797179222</v>
+        <v>0.09916737675666809</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01714107394218445</v>
+        <v>0.254469245672226</v>
       </c>
       <c r="P13" t="n">
-        <v>0.003907773178070784</v>
+        <v>0.1217929944396019</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.005425662267953157</v>
+        <v>0.05811230838298798</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03384135663509369</v>
+        <v>0.1413915753364563</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001978971995413303</v>
+        <v>0.01769465208053589</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01344809401780367</v>
+        <v>0.07421397417783737</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0002436311333440244</v>
+        <v>0.006710543297231197</v>
       </c>
       <c r="V13" t="n">
-        <v>0.006837354507297277</v>
+        <v>0.1253229975700378</v>
       </c>
       <c r="W13" t="n">
-        <v>0.006709367036819458</v>
+        <v>0.1216696724295616</v>
       </c>
       <c r="X13" t="n">
-        <v>0.005206510424613953</v>
+        <v>0.07299767434597015</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.006167396437376738</v>
+        <v>0.01923160627484322</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0003721484681591392</v>
+        <v>0.03468823805451393</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.009693533182144165</v>
+        <v>0.08828569203615189</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.01205255277454853</v>
+        <v>0.05301374197006226</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01143915578722954</v>
+        <v>0.04064370691776276</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.005675937980413437</v>
+        <v>0.07409963011741638</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.003922640811651945</v>
+        <v>0.1197440773248672</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.003059232607483864</v>
+        <v>0.1283006221055984</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01066314056515694</v>
+        <v>0.006042432505637407</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.00243427837267518</v>
+        <v>0.001299003139138222</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0119320061057806</v>
+        <v>0.1606782525777817</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001593943685293198</v>
+        <v>0.04976233094930649</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.009771102108061314</v>
+        <v>0.01937657222151756</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.009441862814128399</v>
+        <v>0.1430109143257141</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.003398334141820669</v>
+        <v>0.0394584946334362</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001234224066138268</v>
+        <v>0.05259989202022552</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.00240776315331459</v>
+        <v>0.09430696815252304</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.004567997995764017</v>
+        <v>0.05970748513936996</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.00590391643345356</v>
+        <v>0.02852042578160763</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.004234996624290943</v>
+        <v>0.0398738905787468</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.004510417580604553</v>
+        <v>0.04159454628825188</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.005322366952896118</v>
+        <v>0.01462936960160732</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.05070935934782028</v>
+        <v>0.4019694328308105</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.007348994258791208</v>
+        <v>0.03027709387242794</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.001799012068659067</v>
+        <v>0.001888787373900414</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0005949684418737888</v>
+        <v>0.009470256976783276</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.007923385128378868</v>
+        <v>0.1796548813581467</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0156291089951992</v>
+        <v>0.02776192501187325</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0100527536123991</v>
+        <v>0.05777071788907051</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.01274232566356659</v>
+        <v>0.009137952700257301</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.005354986526072025</v>
+        <v>0.1355851143598557</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0197868999093771</v>
+        <v>0.1073308363556862</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01078800577670336</v>
+        <v>0.1105697676539421</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0009634171146899462</v>
+        <v>0.0898599773645401</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.02183657884597778</v>
+        <v>0.1085371449589729</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01009705662727356</v>
+        <v>0.007247572764754295</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.005590089596807957</v>
+        <v>0.03851952403783798</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.002784907352179289</v>
+        <v>0.03570272028446198</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01548516005277634</v>
+        <v>0.04995425045490265</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01076921913772821</v>
+        <v>0.02591938897967339</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.001007459126412868</v>
+        <v>0.03846316412091255</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.000474005239084363</v>
+        <v>0.01723447069525719</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01108911633491516</v>
+        <v>0.1070034876465797</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.01960361748933792</v>
+        <v>0.03287279233336449</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01345547940582037</v>
+        <v>0.005917559843510389</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0007890393026173115</v>
+        <v>0.1555311679840088</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.00370684964582324</v>
+        <v>0.0266933161765337</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.003977391868829727</v>
+        <v>0.01220313645899296</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.005474984645843506</v>
+        <v>0.02168991044163704</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02957429923117161</v>
+        <v>0.2678886950016022</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.007656747009605169</v>
+        <v>0.02849170751869678</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.004854508209973574</v>
+        <v>0.1099040359258652</v>
       </c>
       <c r="BY13" t="n">
-        <v>5.229492671787739e-05</v>
+        <v>0.09438729286193848</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.001839156728237867</v>
+        <v>0.1417137980461121</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.002636053366586566</v>
+        <v>0.004089012742042542</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.006164058111608028</v>
+        <v>0.008690109476447105</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0110095888376236</v>
+        <v>0.1176868677139282</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.001491131144575775</v>
+        <v>0.00211750902235508</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01383442711085081</v>
+        <v>0.1181319430470467</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.000449927116278559</v>
+        <v>0.0340445451438427</v>
       </c>
       <c r="CG13" t="n">
-        <v>6.562685302924365e-05</v>
+        <v>0.04325905442237854</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.000163853052072227</v>
+        <v>0.02029027603566647</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0008470200700685382</v>
+        <v>0.03634389489889145</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0006871827645227313</v>
+        <v>0.05117280408740044</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0008699552272446454</v>
+        <v>0.01228006277233362</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.01096388325095177</v>
+        <v>0.0248189102858305</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02222337014973164</v>
+        <v>0.07758235186338425</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01857859268784523</v>
+        <v>0.2023063600063324</v>
       </c>
       <c r="CO13" t="n">
-        <v>9.049367508850992e-05</v>
+        <v>0.1190428212285042</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.005147735122591257</v>
+        <v>0.1103658527135849</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.003260432044044137</v>
+        <v>0.08880916237831116</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.004372305236756802</v>
+        <v>0.009141694754362106</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.01078728213906288</v>
+        <v>0.04171918705105782</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01759573072195053</v>
+        <v>0.01444676239043474</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0007395280990749598</v>
+        <v>0.019986467435956</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001126446295529604</v>
+        <v>0.02632200717926025</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01292860880494118</v>
+        <v>0.1007775589823723</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.001722127315588295</v>
+        <v>0.03454942256212234</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0006979943718761206</v>
+        <v>0.02094697579741478</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.137711271643639e-05</v>
+        <v>0.01866018213331699</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.001118973828852177</v>
+        <v>0.03701513260602951</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0003086599172092974</v>
+        <v>0.04434937238693237</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.001004850375466049</v>
+        <v>0.001666501397266984</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.007685514632612467</v>
+        <v>0.03360173851251602</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.001436141319572926</v>
+        <v>0.1251672506332397</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.006887139286845922</v>
+        <v>0.04919050633907318</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.006419511046260595</v>
+        <v>0.001072999089956284</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.008699364028871059</v>
+        <v>0.1217421889305115</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001390301389619708</v>
+        <v>0.04748310893774033</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.009112648665904999</v>
+        <v>0.1298618167638779</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.009488627314567566</v>
+        <v>0.07676377892494202</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0003254357725381851</v>
+        <v>0.1316150575876236</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.008992810733616352</v>
+        <v>0.02992140129208565</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.000580803956836462</v>
+        <v>0.01292350329458714</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001739816390909255</v>
+        <v>0.03392338752746582</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0083845229819417</v>
+        <v>0.0413108617067337</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.001164932735264301</v>
+        <v>0.06539662182331085</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.001980317523702979</v>
+        <v>0.03585153073072433</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0008410736336372793</v>
+        <v>0.06702230870723724</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0102715352550149</v>
+        <v>0.04629135876893997</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.00142950308509171</v>
+        <v>0.09922289103269577</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.003916030749678612</v>
+        <v>0.05035002157092094</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.00160312233492732</v>
+        <v>0.03019984625279903</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.005538341589272022</v>
+        <v>0.1010637432336807</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.001327333855442703</v>
+        <v>0.08466798067092896</v>
       </c>
       <c r="DZ13" t="n">
-        <v>7.036863826215267e-05</v>
+        <v>0.03732705488801003</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.00401149271056056</v>
+        <v>0.1161302328109741</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0005084255244582891</v>
+        <v>0.1310164332389832</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.002900591120123863</v>
+        <v>0.01419200282543898</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.01401713211089373</v>
+        <v>0.06918279826641083</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0004469472914934158</v>
+        <v>0.08386810123920441</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.003455323865637183</v>
+        <v>0.0410257950425148</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.008242848329246044</v>
+        <v>0.004148973152041435</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.00206020288169384</v>
+        <v>0.008907368406653404</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.006222520489245653</v>
+        <v>0.08583750575780869</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0005028607556596398</v>
+        <v>0.05823218077421188</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.002214728854596615</v>
+        <v>0.02797848172485828</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.006752031855285168</v>
+        <v>0.03503235429525375</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001468624686822295</v>
+        <v>0.0009528445079922676</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.01132896728813648</v>
+        <v>0.01787792332470417</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.00555247999727726</v>
+        <v>0.004981964826583862</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01106789708137512</v>
+        <v>0.08244909346103668</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.004182673990726471</v>
+        <v>0.06398864090442657</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0002115657553076744</v>
+        <v>0.01630830578505993</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.00240369257517159</v>
+        <v>0.03867641091346741</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01022184174507856</v>
+        <v>0.01640740782022476</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.004579993430525064</v>
+        <v>0.004072114825248718</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.005194099619984627</v>
+        <v>0.06924536824226379</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.000666059204377234</v>
+        <v>0.07378579676151276</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0005500853294506669</v>
+        <v>0.005598299205303192</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01432898547500372</v>
+        <v>0.1261972039937973</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0004269314522389323</v>
+        <v>0.0360938161611557</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0005052013439126313</v>
+        <v>0.02835541404783726</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.001721409964375198</v>
+        <v>0.01130194496363401</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.00226501701399684</v>
+        <v>0.04976113885641098</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0003761182306334376</v>
+        <v>0.06189414113759995</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.002933572744950652</v>
+        <v>0.009139550849795341</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.007015392649918795</v>
+        <v>0.03914976492524147</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0004924550885334611</v>
+        <v>0.05478087067604065</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.008383888751268387</v>
+        <v>0.06602077186107635</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.004834802821278572</v>
+        <v>0.01228923816233873</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.006689074449241161</v>
+        <v>0.01937995851039886</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.00606954051181674</v>
+        <v>0.05304127931594849</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.004775943234562874</v>
+        <v>0.02068948745727539</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.002575150225311518</v>
+        <v>0.03462234511971474</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.001752102049067616</v>
+        <v>0.1437200158834457</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.004066433291882277</v>
+        <v>0.07916530221700668</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.007664856966584921</v>
+        <v>0.1133994981646538</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01485299039632082</v>
+        <v>0.1421623080968857</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.001617105910554528</v>
+        <v>0.01108037680387497</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.003866688115522265</v>
+        <v>0.08317072689533234</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.00194057053886354</v>
+        <v>0.0402313806116581</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001604400691576302</v>
+        <v>0.09732583165168762</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01312229223549366</v>
+        <v>0.001497548073530197</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.01472056098282337</v>
+        <v>0.1871597021818161</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.006538316607475281</v>
+        <v>0.06454689800739288</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01246759574860334</v>
+        <v>0.008084644563496113</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.005290868226438761</v>
+        <v>0.004557800013571978</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.005568495951592922</v>
+        <v>0.05540946871042252</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.007213969249278307</v>
+        <v>0.008874909020960331</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01166691537946463</v>
+        <v>0.06574671715497971</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.00988200306892395</v>
+        <v>0.08651856333017349</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.01102328859269619</v>
+        <v>0.01710055023431778</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.01240583322942257</v>
+        <v>0.05035780370235443</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.00234663556329906</v>
+        <v>0.06965607404708862</v>
       </c>
     </row>
     <row r="14">
@@ -8396,2278 +8396,2278 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.088435098528862</v>
+        <v>0.2687762379646301</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8916751742362976</v>
+        <v>0.6226202249526978</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7573051452636719</v>
+        <v>0.3275626301765442</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3312286138534546</v>
+        <v>0.2039746344089508</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2099039554595947</v>
+        <v>0.2267170995473862</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1365602910518646</v>
+        <v>0.1694556623697281</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2032173573970795</v>
+        <v>0.2088228911161423</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1227013021707535</v>
+        <v>0.1215227246284485</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3958770632743835</v>
+        <v>0.2022266238927841</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2006846368312836</v>
+        <v>0.179391086101532</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6999743580818176</v>
+        <v>0.8532198667526245</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6932139992713928</v>
+        <v>0.2611278593540192</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4416895508766174</v>
+        <v>0.08365171402692795</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7111559510231018</v>
+        <v>0.1754727065563202</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2699916660785675</v>
+        <v>0.05508749186992645</v>
       </c>
       <c r="P15" t="n">
-        <v>0.01694869995117188</v>
+        <v>0.274592399597168</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.04623906314373016</v>
+        <v>0.0003347247838973999</v>
       </c>
       <c r="R15" t="n">
-        <v>0.310087651014328</v>
+        <v>0.05064806342124939</v>
       </c>
       <c r="S15" t="n">
-        <v>0.01456266175955534</v>
+        <v>0.008044570684432983</v>
       </c>
       <c r="T15" t="n">
-        <v>0.09760099649429321</v>
+        <v>0.255477100610733</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07389794290065765</v>
+        <v>0.1964902579784393</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1813606023788452</v>
+        <v>0.1503680646419525</v>
       </c>
       <c r="W15" t="n">
-        <v>0.002290621399879456</v>
+        <v>0.0511147528886795</v>
       </c>
       <c r="X15" t="n">
-        <v>0.06288929283618927</v>
+        <v>0.04046995565295219</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.004862808156758547</v>
+        <v>0.0003152545541524887</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.05449917167425156</v>
+        <v>0.03889816999435425</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1343504786491394</v>
+        <v>0.1754651218652725</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.04732516407966614</v>
+        <v>0.2441706359386444</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2542881667613983</v>
+        <v>0.005385860800743103</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02267815172672272</v>
+        <v>0.2945399284362793</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.07311035692691803</v>
+        <v>0.2713527083396912</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.2935304343700409</v>
+        <v>0.2591636478900909</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.180426150560379</v>
+        <v>0.02028688788414001</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.04947018623352051</v>
+        <v>0.03641752898693085</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.2040415555238724</v>
+        <v>0.2945728302001953</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.004792877472937107</v>
+        <v>0.08983665704727173</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.04584190249443054</v>
+        <v>0.04869481921195984</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.3421925604343414</v>
+        <v>0.4405748844146729</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.05882570520043373</v>
+        <v>0.004134617745876312</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.03409725055098534</v>
+        <v>0.04040418565273285</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.003768936265259981</v>
+        <v>0.5076596736907959</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1957720220088959</v>
+        <v>0.0308260302990675</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.05994898825883865</v>
+        <v>0.01749100349843502</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.1349697262048721</v>
+        <v>0.1287878155708313</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.1456124633550644</v>
+        <v>0.09811882674694061</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.1549188494682312</v>
+        <v>0.09124419093132019</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.6671390533447266</v>
+        <v>0.7517727613449097</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3621934652328491</v>
+        <v>0.1080253794789314</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.01883494853973389</v>
+        <v>0.1724483072757721</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.2600140869617462</v>
+        <v>0.1451749503612518</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.2097503542900085</v>
+        <v>0.002314627170562744</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.03261479735374451</v>
+        <v>0.02609948441386223</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.08539937436580658</v>
+        <v>0.1648499816656113</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.1195805743336678</v>
+        <v>0.002348165959119797</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0304252989590168</v>
+        <v>0.0926402360200882</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.131457507610321</v>
+        <v>0.5040830373764038</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.2520756721496582</v>
+        <v>0.3207319378852844</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.3046805858612061</v>
+        <v>0.1432682871818542</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.6729714870452881</v>
+        <v>0.8251618146896362</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.1507252603769302</v>
+        <v>0.02655309811234474</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.02363672479987144</v>
+        <v>0.1223786398768425</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.17696513235569</v>
+        <v>0.1420284658670425</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.1096611842513084</v>
+        <v>0.06198404729366302</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.2289341390132904</v>
+        <v>0.001290071755647659</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1363718211650848</v>
+        <v>0.1230034008622169</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.125138059258461</v>
+        <v>0.02520387247204781</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.07394221425056458</v>
+        <v>0.04577242210507393</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.2857711017131805</v>
+        <v>0.1909235715866089</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.1661810576915741</v>
+        <v>0.05285172536969185</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.1886033713817596</v>
+        <v>0.1986739486455917</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.002013008110225201</v>
+        <v>0.01547740772366524</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.185329258441925</v>
+        <v>0.102634035050869</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.07743279635906219</v>
+        <v>0.08321357518434525</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2316778302192688</v>
+        <v>0.6350379586219788</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.4213011264801025</v>
+        <v>0.09945349395275116</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.03769047185778618</v>
+        <v>0.06918965280056</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.05859482660889626</v>
+        <v>0.06492675840854645</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.08062558621168137</v>
+        <v>0.06610564887523651</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.1012281253933907</v>
+        <v>0.04599051177501678</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.05263250693678856</v>
+        <v>0.03439736366271973</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.01380965299904346</v>
+        <v>0.1127715483307838</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.01332512870430946</v>
+        <v>0.004153918474912643</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1876080632209778</v>
+        <v>0.303742378950119</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0653170719742775</v>
+        <v>0.08200336247682571</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.1426530182361603</v>
+        <v>0.0684305876493454</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.05313464254140854</v>
+        <v>0.02346606366336346</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.04677149653434753</v>
+        <v>0.03975712135434151</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.02438976988196373</v>
+        <v>0.03531613573431969</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.07523840665817261</v>
+        <v>0.006553836166858673</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.1391625851392746</v>
+        <v>0.007193021476268768</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.2568032145500183</v>
+        <v>0.2772261202335358</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.05776631832122803</v>
+        <v>0.2197984158992767</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.01805334538221359</v>
+        <v>0.01698587276041508</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.2121564149856567</v>
+        <v>0.3387152850627899</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.2487082928419113</v>
+        <v>0.5684077739715576</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.126150369644165</v>
+        <v>0.005166523158550262</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.112414076924324</v>
+        <v>0.1189189255237579</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0262702964246273</v>
+        <v>0.1796172857284546</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.004898899234831333</v>
+        <v>0.0798591822385788</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.03826592862606049</v>
+        <v>0.03673702478408813</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.132415696978569</v>
+        <v>0.2656436562538147</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.06088648363947868</v>
+        <v>0.06091897189617157</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.1066724061965942</v>
+        <v>0.04702822864055634</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.03676606714725494</v>
+        <v>0.0330318808555603</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.04591641947627068</v>
+        <v>0.07039454579353333</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.01465154625475407</v>
+        <v>0.005761559121310711</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.06213361024856567</v>
+        <v>0.0311965849250555</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.1707697957754135</v>
+        <v>0.06512451171875</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.1381375938653946</v>
+        <v>0.1981281936168671</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1381270289421082</v>
+        <v>0.1486849337816238</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.009530536830425262</v>
+        <v>0.1324305981397629</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.2152276039123535</v>
+        <v>0.009573996067047119</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1917528957128525</v>
+        <v>0.1947003751993179</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.02970944344997406</v>
+        <v>0.6044449210166931</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.01731787621974945</v>
+        <v>0.008657140657305717</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.1083799079060555</v>
+        <v>0.04969605058431625</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.06079533323645592</v>
+        <v>0.08813938498497009</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.03845728561282158</v>
+        <v>0.01924204081296921</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.02156985737383366</v>
+        <v>0.1486398875713348</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1073613166809082</v>
+        <v>0.05209465324878693</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.1465788632631302</v>
+        <v>0.06624189764261246</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1479945778846741</v>
+        <v>0.05146843940019608</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.03820781037211418</v>
+        <v>0.255109965801239</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1423766016960144</v>
+        <v>0.0299975760281086</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.1522340029478073</v>
+        <v>0.1358433961868286</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.08131760358810425</v>
+        <v>0.08639191091060638</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.09999288618564606</v>
+        <v>0.06938432157039642</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.02543755620718002</v>
+        <v>0.2058709710836411</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.04621727019548416</v>
+        <v>0.06203243508934975</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0791490226984024</v>
+        <v>0.0005117543041706085</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.09376154839992523</v>
+        <v>0.1539427638053894</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.2802650630474091</v>
+        <v>0.3203111886978149</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.01739141717553139</v>
+        <v>0.06307515501976013</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.008438372053205967</v>
+        <v>0.04349420219659805</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.06823921203613281</v>
+        <v>0.1415251344442368</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.003063610289245844</v>
+        <v>0.01835619658231735</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0775047168135643</v>
+        <v>0.09360369294881821</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.08607800304889679</v>
+        <v>0.07515764981508255</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.05292937904596329</v>
+        <v>0.1569285690784454</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1091387271881104</v>
+        <v>0.02895081415772438</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.000465495279058814</v>
+        <v>0.02814450673758984</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.1364296078681946</v>
+        <v>0.007024121470749378</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.08940383791923523</v>
+        <v>0.01957234181463718</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.1739387810230255</v>
+        <v>0.05744874477386475</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.03373361378908157</v>
+        <v>0.06796343624591827</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.1182961463928223</v>
+        <v>0.1992215067148209</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.06053688377141953</v>
+        <v>0.07694841921329498</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.06686276197433472</v>
+        <v>0.02890896424651146</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.04180433973670006</v>
+        <v>0.01904100365936756</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.1116486489772797</v>
+        <v>0.06097357720136642</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.1653341799974442</v>
+        <v>0.02411635778844357</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.0704343393445015</v>
+        <v>0.05062906444072723</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.3515022099018097</v>
+        <v>0.0464216060936451</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.01222024857997894</v>
+        <v>0.0003886967897415161</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1355529874563217</v>
+        <v>0.3074817657470703</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.05308847874403</v>
+        <v>0.06921613216400146</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.1313017457723618</v>
+        <v>0.04311375319957733</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.07490745931863785</v>
+        <v>0.04920691251754761</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01214241143316031</v>
+        <v>0.1008251532912254</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.01329905539751053</v>
+        <v>0.04304481670260429</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.1160469576716423</v>
+        <v>0.01485060527920723</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.1102082505822182</v>
+        <v>0.03976887464523315</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.08376200497150421</v>
+        <v>0.03596266359090805</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.1418160498142242</v>
+        <v>0.07190500199794769</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1854183077812195</v>
+        <v>0.1277748495340347</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.005983561277389526</v>
+        <v>0.007714778184890747</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.2019547671079636</v>
+        <v>0.2381382882595062</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.04320807009935379</v>
+        <v>0.1732509434223175</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.1605877280235291</v>
+        <v>0.01154648512601852</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.1071725636720657</v>
+        <v>0.1801286935806274</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.1090638041496277</v>
+        <v>0.168864518404007</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.004149392247200012</v>
+        <v>0.2964589595794678</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.1437287032604218</v>
+        <v>0.0761253759264946</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.2950272560119629</v>
+        <v>0.04936354607343674</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1876003444194794</v>
+        <v>0.02998275868594646</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.001220013946294785</v>
+        <v>0.1289011090993881</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.03043168038129807</v>
+        <v>0.3055893778800964</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.1744626462459564</v>
+        <v>0.02460561692714691</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.1828101575374603</v>
+        <v>0.1081967577338219</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.04834791272878647</v>
+        <v>0.1094190254807472</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.1499404311180115</v>
+        <v>0.05453035235404968</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.03553764894604683</v>
+        <v>0.07251079380512238</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.03584712743759155</v>
+        <v>0.1297701597213745</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.2561672031879425</v>
+        <v>0.08556094765663147</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.05124550312757492</v>
+        <v>0.02827074378728867</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.3023892939090729</v>
+        <v>0.1456793993711472</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.1050197705626488</v>
+        <v>0.02079485170543194</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.4624808430671692</v>
+        <v>0.1125335544347763</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.04136498272418976</v>
+        <v>0.122537724673748</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.0001631181658012792</v>
+        <v>0.001170914620161057</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001889335573650897</v>
+        <v>0.03537476062774658</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001668090262683108</v>
+        <v>0.01628318428993225</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0006202576332725585</v>
+        <v>0.009156850166618824</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0005062422133050859</v>
+        <v>0.005885117221623659</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0008933903882279992</v>
+        <v>0.02683816105127335</v>
       </c>
       <c r="G16" t="n">
-        <v>2.122368096024729e-05</v>
+        <v>0.00834188237786293</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005238043959252536</v>
+        <v>0.007337002549320459</v>
       </c>
       <c r="I16" t="n">
-        <v>3.937230758310761e-06</v>
+        <v>0.01437326427549124</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0003159629413858056</v>
+        <v>0.004702054429799318</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001763940206728876</v>
+        <v>0.0324048176407814</v>
       </c>
       <c r="L16" t="n">
-        <v>2.487436540832277e-05</v>
+        <v>0.02165296114981174</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0003787704044952989</v>
+        <v>0.02529784291982651</v>
       </c>
       <c r="N16" t="n">
-        <v>6.062746251700446e-05</v>
+        <v>0.005261767655611038</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0009548652451485395</v>
+        <v>0.03220780938863754</v>
       </c>
       <c r="P16" t="n">
-        <v>4.206172889098525e-06</v>
+        <v>0.008857348002493382</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.000162035139510408</v>
+        <v>0.001031881663948298</v>
       </c>
       <c r="R16" t="n">
-        <v>6.340137770166621e-05</v>
+        <v>0.01869688369333744</v>
       </c>
       <c r="S16" t="n">
-        <v>5.778417107649148e-05</v>
+        <v>0.004868017975240946</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0001470395072828978</v>
+        <v>0.008857017382979393</v>
       </c>
       <c r="U16" t="n">
-        <v>7.867005479056388e-05</v>
+        <v>0.001924076583236456</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0002334041200811043</v>
+        <v>0.002391816349700093</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0001604351418791339</v>
+        <v>0.00291938753798604</v>
       </c>
       <c r="X16" t="n">
-        <v>2.668241540959571e-05</v>
+        <v>0.001088885706849396</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.063694359501824e-05</v>
+        <v>0.006426462437957525</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0001636910455999896</v>
+        <v>0.002282130066305399</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.545915337279439e-05</v>
+        <v>0.004282251931726933</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.59093358181417e-05</v>
+        <v>0.003937005996704102</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.759794814570341e-06</v>
+        <v>0.001434599864296615</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.052860483876429e-05</v>
+        <v>0.008841199800372124</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0001341817405773327</v>
+        <v>0.009676471352577209</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0001374992716591805</v>
+        <v>0.008799603208899498</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.170685183955356e-05</v>
+        <v>0.01572690159082413</v>
       </c>
       <c r="AH16" t="n">
-        <v>4.709996210294776e-05</v>
+        <v>0.002816773019731045</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0001083903480321169</v>
+        <v>0.02490947395563126</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0001226260210387409</v>
+        <v>0.001037344569340348</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.000315203593345359</v>
+        <v>0.0036312744487077</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0001255485694855452</v>
+        <v>0.007059879135340452</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.97851838695351e-05</v>
+        <v>6.447546184062958e-06</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.8976119463332e-05</v>
+        <v>0.003232626942917705</v>
       </c>
       <c r="AO16" t="n">
-        <v>5.651088213198818e-05</v>
+        <v>0.004336984362453222</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0002604001783765852</v>
+        <v>0.003574779722839594</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.439535016193986e-05</v>
+        <v>0.0004007230745628476</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0001606038713362068</v>
+        <v>0.008831175044178963</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0002110010100295767</v>
+        <v>0.003208555281162262</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.611798067344353e-05</v>
+        <v>0.004545091185718775</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.001012469059787691</v>
+        <v>0.03294645994901657</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.0002355398901272565</v>
+        <v>0.01117176283150911</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.383124178275466e-06</v>
+        <v>0.009016102179884911</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.000290874857455492</v>
+        <v>0.01689797453582287</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0004278796259313822</v>
+        <v>0.02356120571494102</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7.924743840703741e-05</v>
+        <v>0.002055190969258547</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.0002002502878895029</v>
+        <v>0.009953182190656662</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.000166278550750576</v>
+        <v>0.003395111300051212</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.376138920430094e-05</v>
+        <v>0.005298375152051449</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.000406842038501054</v>
+        <v>0.005488956347107887</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0004848832322750241</v>
+        <v>0.0102805569767952</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.934165478218347e-05</v>
+        <v>0.003270747140049934</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0001632343046367168</v>
+        <v>0.01290745660662651</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.0001118674990721047</v>
+        <v>0.004394046496599913</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0001115993363782763</v>
+        <v>0.008007928729057312</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.0001129989686887711</v>
+        <v>0.000158480484969914</v>
       </c>
       <c r="BK16" t="n">
-        <v>7.634709618287161e-05</v>
+        <v>0.00931285135447979</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0001267630723305047</v>
+        <v>0.000703361292835325</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0002111915091518313</v>
+        <v>0.0103660486638546</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.000210797501495108</v>
+        <v>0.006786804646253586</v>
       </c>
       <c r="BO16" t="n">
-        <v>7.818379526725039e-05</v>
+        <v>0.002731929300352931</v>
       </c>
       <c r="BP16" t="n">
-        <v>7.37597729312256e-05</v>
+        <v>0.003509191796183586</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.603511115419678e-05</v>
+        <v>0.006545693147927523</v>
       </c>
       <c r="BR16" t="n">
-        <v>4.865483788307756e-05</v>
+        <v>0.005328189115971327</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.601972902193666e-05</v>
+        <v>0.00101827026810497</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.0002356663899263367</v>
+        <v>0.003091130405664444</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.243096216465347e-05</v>
+        <v>0.001995916711166501</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0006328243762254715</v>
+        <v>0.02317385748028755</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.0001935378677444533</v>
+        <v>0.002974882256239653</v>
       </c>
       <c r="BX16" t="n">
-        <v>3.565770748537034e-05</v>
+        <v>0.00487053208053112</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0001070861326297745</v>
+        <v>0.002387237967923284</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.0002413707552477717</v>
+        <v>0.009261568076908588</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.260387504473329e-05</v>
+        <v>0.01054249703884125</v>
       </c>
       <c r="CB16" t="n">
-        <v>9.238642815034837e-05</v>
+        <v>0.0006352164782583714</v>
       </c>
       <c r="CC16" t="n">
-        <v>8.944071305450052e-05</v>
+        <v>0.004311577416956425</v>
       </c>
       <c r="CD16" t="n">
-        <v>5.237705772742629e-05</v>
+        <v>0.0004465966485440731</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0003552263078745455</v>
+        <v>0.01198937185108662</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.0001334794942522421</v>
+        <v>0.005373727530241013</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.000100217257568147</v>
+        <v>0.003378112334758043</v>
       </c>
       <c r="CH16" t="n">
-        <v>8.533026266377419e-05</v>
+        <v>0.0005961578572168946</v>
       </c>
       <c r="CI16" t="n">
-        <v>6.177782779559493e-05</v>
+        <v>0.005380411166697741</v>
       </c>
       <c r="CJ16" t="n">
-        <v>9.604453225620091e-05</v>
+        <v>9.748214506544173e-05</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.0001121832829085179</v>
+        <v>0.001011554268188775</v>
       </c>
       <c r="CL16" t="n">
-        <v>9.568981477059424e-05</v>
+        <v>0.001950723817571998</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0004060997162014246</v>
+        <v>0.004640004597604275</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0001427193928975612</v>
+        <v>0.005664209835231304</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.067832999979146e-05</v>
+        <v>0.009152412414550781</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0002944590232800692</v>
+        <v>0.01309758890420198</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.000269729207502678</v>
+        <v>0.004663063678890467</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.000475928740343079</v>
+        <v>0.00690039386972785</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0003509453381411731</v>
+        <v>0.005879075266420841</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.0001534642797196284</v>
+        <v>0.0009333047783002257</v>
       </c>
       <c r="CU16" t="n">
-        <v>6.687518180115148e-05</v>
+        <v>0.005705111194401979</v>
       </c>
       <c r="CV16" t="n">
-        <v>4.686772808781825e-05</v>
+        <v>0.002814669394865632</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0003457935526967049</v>
+        <v>0.009811547584831715</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0001857899769674987</v>
+        <v>0.007318746298551559</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0001760130107868463</v>
+        <v>0.00480924267321825</v>
       </c>
       <c r="CZ16" t="n">
-        <v>6.980042235227302e-05</v>
+        <v>0.00125197833403945</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0001013039582176134</v>
+        <v>0.008281609043478966</v>
       </c>
       <c r="DB16" t="n">
-        <v>7.840368198230863e-05</v>
+        <v>0.001391322119161487</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0002136842958861962</v>
+        <v>0.001083993120118976</v>
       </c>
       <c r="DD16" t="n">
-        <v>7.674968219362199e-05</v>
+        <v>0.002800433663651347</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.0001854291040217504</v>
+        <v>0.00119382981210947</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0001358614681521431</v>
+        <v>0.02199529111385345</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.657517714193091e-05</v>
+        <v>0.01390496548265219</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0005935899680480361</v>
+        <v>0.0004245604213792831</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0007079532369971275</v>
+        <v>0.005767093505710363</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0001573245681356639</v>
+        <v>0.01836448907852173</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.0002658727462403476</v>
+        <v>0.00461293151602149</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0002777804038487375</v>
+        <v>0.0102550620213151</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0002659239689819515</v>
+        <v>0.002553027821704745</v>
       </c>
       <c r="DN16" t="n">
-        <v>9.680886432761326e-05</v>
+        <v>0.002103353850543499</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0002035030047409236</v>
+        <v>0.009962008334696293</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.0001132723773480393</v>
+        <v>0.003189150476828218</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0002021978434640914</v>
+        <v>0.008779753930866718</v>
       </c>
       <c r="DR16" t="n">
-        <v>2.729173320403788e-05</v>
+        <v>0.0007775256526656449</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0001303450844716281</v>
+        <v>0.005791104398667812</v>
       </c>
       <c r="DT16" t="n">
-        <v>7.313933747354895e-05</v>
+        <v>0.003756608814001083</v>
       </c>
       <c r="DU16" t="n">
-        <v>7.107741839718074e-05</v>
+        <v>0.00907464511692524</v>
       </c>
       <c r="DV16" t="n">
-        <v>0.0001051186700351536</v>
+        <v>0.003691642777994275</v>
       </c>
       <c r="DW16" t="n">
-        <v>1.073316525435075e-05</v>
+        <v>4.444236401468515e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>8.342448563780636e-05</v>
+        <v>0.007355325855314732</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.000190667255083099</v>
+        <v>0.01434815675020218</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2.904977736761793e-05</v>
+        <v>0.002764844801276922</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0001145925925811753</v>
+        <v>0.005015077069401741</v>
       </c>
       <c r="EB16" t="n">
-        <v>7.418404857162386e-05</v>
+        <v>0.001806750427931547</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.0001109280274249613</v>
+        <v>0.01077017933130264</v>
       </c>
       <c r="ED16" t="n">
-        <v>4.2526371544227e-05</v>
+        <v>0.005345709621906281</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.0001240818237420171</v>
+        <v>0.01891810074448586</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.0002907193847931921</v>
+        <v>0.000287853617919609</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.000389825931051746</v>
+        <v>0.0002521926071494818</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0002340539067517966</v>
+        <v>0.0001075002364814281</v>
       </c>
       <c r="EI16" t="n">
-        <v>9.900775330606848e-05</v>
+        <v>0.0109094362705946</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.000102222191344481</v>
+        <v>0.0001466491958126426</v>
       </c>
       <c r="EK16" t="n">
-        <v>8.934622746892273e-05</v>
+        <v>0.001051033497788012</v>
       </c>
       <c r="EL16" t="n">
-        <v>5.137198604643345e-05</v>
+        <v>0.002515410538762808</v>
       </c>
       <c r="EM16" t="n">
-        <v>2.587077506177593e-05</v>
+        <v>0.003547556698322296</v>
       </c>
       <c r="EN16" t="n">
-        <v>3.026127706107218e-05</v>
+        <v>0.009404611773788929</v>
       </c>
       <c r="EO16" t="n">
-        <v>4.475095920497552e-05</v>
+        <v>0.002818424720317125</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.0001681698195170611</v>
+        <v>0.008476853370666504</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0001980321103474125</v>
+        <v>0.003107764991000295</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0001700302673270926</v>
+        <v>0.004350848961621523</v>
       </c>
       <c r="ES16" t="n">
-        <v>9.772025805432349e-05</v>
+        <v>0.007099224720150232</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.0002633362601045519</v>
+        <v>0.009361130185425282</v>
       </c>
       <c r="EU16" t="n">
-        <v>0.0001939963258337229</v>
+        <v>0.00119701842777431</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.0004204581491649151</v>
+        <v>7.978489156812429e-05</v>
       </c>
       <c r="EW16" t="n">
-        <v>7.263838779181242e-05</v>
+        <v>0.001520178746432066</v>
       </c>
       <c r="EX16" t="n">
-        <v>7.955156615935266e-05</v>
+        <v>0.001138753606937826</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0003238018252886832</v>
+        <v>0.01279108040034771</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.0001497794582974166</v>
+        <v>0.003964819945394993</v>
       </c>
       <c r="FA16" t="n">
-        <v>9.440102439839393e-05</v>
+        <v>0.005548203829675913</v>
       </c>
       <c r="FB16" t="n">
-        <v>7.331310916924849e-05</v>
+        <v>0.001100726192817092</v>
       </c>
       <c r="FC16" t="n">
-        <v>7.212588388938457e-05</v>
+        <v>0.006619445513933897</v>
       </c>
       <c r="FD16" t="n">
-        <v>0.0001129485535784625</v>
+        <v>0.001433333498425782</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0001809921959647909</v>
+        <v>0.0008237179717980325</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.000111073961306829</v>
+        <v>0.004400006029754877</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.000102160673122853</v>
+        <v>0.003001033328473568</v>
       </c>
       <c r="FH16" t="n">
-        <v>2.01089051188319e-06</v>
+        <v>0.001852722954936326</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0002904756984207779</v>
+        <v>0.007819363847374916</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.0002359157806495205</v>
+        <v>0.002588840899989009</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.000143042765557766</v>
+        <v>0.002198558067902923</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.0002023005217779428</v>
+        <v>0.01106899790465832</v>
       </c>
       <c r="FM16" t="n">
-        <v>1.280935612157919e-05</v>
+        <v>0.002302519977092743</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.0001257928815903142</v>
+        <v>0.009683148935437202</v>
       </c>
       <c r="FO16" t="n">
-        <v>9.641298674978316e-05</v>
+        <v>0.02058874815702438</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0002638536388985813</v>
+        <v>0.001219585537910461</v>
       </c>
       <c r="FQ16" t="n">
-        <v>3.116457264695782e-06</v>
+        <v>0.006315313745290041</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.0003567537933122367</v>
+        <v>0.003256276715546846</v>
       </c>
       <c r="FS16" t="n">
-        <v>1.024649100145325e-05</v>
+        <v>0.003777916310355067</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.0002086150052491575</v>
+        <v>0.006203638855367899</v>
       </c>
       <c r="FU16" t="n">
-        <v>9.27250730455853e-05</v>
+        <v>0.00268095824867487</v>
       </c>
       <c r="FV16" t="n">
-        <v>8.756144234212115e-05</v>
+        <v>0.002905052620917559</v>
       </c>
       <c r="FW16" t="n">
-        <v>7.449685654137284e-06</v>
+        <v>0.02529685199260712</v>
       </c>
       <c r="FX16" t="n">
-        <v>3.51199705619365e-05</v>
+        <v>0.003618353512138128</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0003085836942773312</v>
+        <v>0.002173455897718668</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0001325631310464814</v>
+        <v>0.0031074492726475</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.0001932467421283945</v>
+        <v>0.01654097065329552</v>
       </c>
       <c r="GB16" t="n">
-        <v>2.301100539625622e-05</v>
+        <v>0.002092641312628984</v>
       </c>
       <c r="GC16" t="n">
-        <v>2.485270670149475e-06</v>
+        <v>0.01566447876393795</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.00021666671091225</v>
+        <v>0.008371374569833279</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.0004234141670167446</v>
+        <v>0.006406196858733892</v>
       </c>
       <c r="GF16" t="n">
-        <v>7.103556708898395e-05</v>
+        <v>0.003060371382161975</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0002216167631559074</v>
+        <v>0.001645276322960854</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8.117115066852421e-05</v>
+        <v>2.275499233483913e-10</v>
       </c>
       <c r="B17" t="n">
-        <v>0.006788062397390604</v>
+        <v>8.32563462616065e-10</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0005202685133554041</v>
+        <v>2.679777511005454e-10</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001672831480391324</v>
+        <v>3.573983886617782e-10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002247411059215665</v>
+        <v>1.456099268937194e-10</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001343720708973706</v>
+        <v>7.68738739331809e-10</v>
       </c>
       <c r="G17" t="n">
-        <v>6.129976827651262e-05</v>
+        <v>2.376693286620934e-11</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001024784753099084</v>
+        <v>4.83042050802851e-10</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0001426123344572261</v>
+        <v>4.771736339392874e-10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0003562650235835463</v>
+        <v>2.95750757217661e-10</v>
       </c>
       <c r="K17" t="n">
-        <v>0.005851478781551123</v>
+        <v>9.274496726163761e-10</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0003411334182601422</v>
+        <v>2.601952542313768e-10</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0008274443680420518</v>
+        <v>2.804848020510065e-10</v>
       </c>
       <c r="N17" t="n">
-        <v>0.001412294339388609</v>
+        <v>1.626556389577871e-10</v>
       </c>
       <c r="O17" t="n">
-        <v>0.001339037087745965</v>
+        <v>7.346084851533874e-10</v>
       </c>
       <c r="P17" t="n">
-        <v>8.717653690837324e-05</v>
+        <v>8.29661617185451e-11</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0001254177186638117</v>
+        <v>5.517855061754062e-10</v>
       </c>
       <c r="R17" t="n">
-        <v>3.894808833138086e-05</v>
+        <v>1.637231183959642e-10</v>
       </c>
       <c r="S17" t="n">
-        <v>9.907063213177025e-05</v>
+        <v>2.108922481092179e-10</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0006956873694434762</v>
+        <v>9.737309569768371e-11</v>
       </c>
       <c r="U17" t="n">
-        <v>0.000210482714464888</v>
+        <v>4.680886928065675e-11</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0007009138353168964</v>
+        <v>7.199570800642263e-11</v>
       </c>
       <c r="W17" t="n">
-        <v>0.001254660077393055</v>
+        <v>1.078273928478701e-11</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0002848459698725492</v>
+        <v>1.22858279105742e-10</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.000166105484822765</v>
+        <v>8.766738029963861e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.001234636292792857</v>
+        <v>1.638128521719295e-10</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0004192389314994216</v>
+        <v>1.341098343488056e-10</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.000176253350218758</v>
+        <v>2.108119581678558e-11</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0002696577284950763</v>
+        <v>1.043997527316876e-10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0003460457955952734</v>
+        <v>2.681899702317025e-10</v>
       </c>
       <c r="AE17" t="n">
-        <v>7.749452925054356e-05</v>
+        <v>2.058253428804946e-10</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0003656554326880723</v>
+        <v>6.509703887047635e-11</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0001504960091551766</v>
+        <v>1.985757114297826e-10</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.311002339818515e-05</v>
+        <v>2.086028572101384e-11</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0003695377963595092</v>
+        <v>2.136995302937095e-10</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0005672528059221804</v>
+        <v>3.825037786509e-10</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0009708751458674669</v>
+        <v>2.712483015976375e-10</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0006354301003739238</v>
+        <v>3.841477830279771e-11</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0001166855145129375</v>
+        <v>2.158802858698294e-10</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0001522952516097575</v>
+        <v>4.348447990576432e-11</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0006270452286116779</v>
+        <v>4.808639944564597e-11</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0005243479972705245</v>
+        <v>1.165023199439785e-11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.068192695034668e-05</v>
+        <v>2.101755748606937e-11</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0002443056146148592</v>
+        <v>1.14425986047495e-11</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0002049975009867921</v>
+        <v>1.632526579198323e-11</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.546442455146462e-05</v>
+        <v>4.433862721420212e-10</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.004267036449164152</v>
+        <v>8.765044245961917e-12</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0001437949540559202</v>
+        <v>2.448944935729003e-10</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0002683326310943812</v>
+        <v>1.217472789249996e-10</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0009986970108002424</v>
+        <v>5.542011294323856e-10</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.000655911338981241</v>
+        <v>2.033095913844818e-10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0003605915699154139</v>
+        <v>1.637257274200721e-10</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0001485201646573842</v>
+        <v>2.470585021285832e-11</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.0001109309232560918</v>
+        <v>1.494325219120185e-10</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.0004173951456323266</v>
+        <v>2.30829452774195e-10</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.001629539066925645</v>
+        <v>5.40292810491394e-10</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.001033445238135755</v>
+        <v>1.392307380498892e-10</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0002355108445044607</v>
+        <v>2.65448107938937e-10</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.001420099288225174</v>
+        <v>7.025044435060579e-10</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0006453137029893696</v>
+        <v>2.193368264791218e-10</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0003724122070707381</v>
+        <v>7.576066163306194e-11</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0002631075331009924</v>
+        <v>2.193923098747774e-10</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.0001999879750655964</v>
+        <v>5.963665117292294e-10</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0006107053486630321</v>
+        <v>7.211413410868062e-11</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.001155867241322994</v>
+        <v>1.330764110019089e-10</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.000624251551926136</v>
+        <v>1.142352878957809e-11</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0001084687100956216</v>
+        <v>9.839332126837519e-11</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0005750969867222011</v>
+        <v>6.366753652065071e-11</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0001013930304907262</v>
+        <v>1.057489304456816e-10</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0001757729332894087</v>
+        <v>2.15783196866326e-10</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.0002464959397912025</v>
+        <v>6.60093993354316e-11</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0003909982042387128</v>
+        <v>1.223709189535072e-10</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.0001433812431059778</v>
+        <v>3.651716151686912e-10</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.002440851414576173</v>
+        <v>3.400453529867065e-11</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0005644572665914893</v>
+        <v>7.375093591388548e-12</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.0002264044451294467</v>
+        <v>9.727475075438363e-11</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0004995109047740698</v>
+        <v>9.998688682566481e-11</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0001882829674286768</v>
+        <v>5.211621412204437e-11</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0002947131870314479</v>
+        <v>1.728402143630348e-11</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0001659547269809991</v>
+        <v>7.271122592911183e-11</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.000253308069659397</v>
+        <v>6.24764129319999e-12</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0001349720550933853</v>
+        <v>4.785622245706556e-11</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.00103107385803014</v>
+        <v>1.739933197519861e-10</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0002836918574757874</v>
+        <v>2.854705014043724e-11</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0002452794287819415</v>
+        <v>5.347971371305604e-11</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0001308146020164713</v>
+        <v>1.214815192884799e-10</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.0001317678834311664</v>
+        <v>2.186720249319762e-10</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0003341020783409476</v>
+        <v>6.966785481843374e-11</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0001960750669240952</v>
+        <v>5.618482068481256e-11</v>
       </c>
       <c r="CL17" t="n">
-        <v>9.002475417219102e-05</v>
+        <v>7.225639531149852e-11</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.00148152292240411</v>
+        <v>6.206878067072097e-11</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0005389873986132443</v>
+        <v>1.160405105338214e-10</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0001981304958462715</v>
+        <v>2.444688063096834e-10</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0005463762208819389</v>
+        <v>6.458428236655323e-11</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.000784562318585813</v>
+        <v>2.963725376226023e-10</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0007044312660582364</v>
+        <v>3.039743456945132e-11</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.001118994667194784</v>
+        <v>6.316977496645393e-11</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0007002639467827976</v>
+        <v>5.962423610395007e-11</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0003045173361897469</v>
+        <v>2.366135343212505e-10</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0001028082624543458</v>
+        <v>8.191036043880828e-11</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0009183087386190891</v>
+        <v>1.859216253174978e-10</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0003545683284755796</v>
+        <v>3.365377421182814e-11</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0004865524533670396</v>
+        <v>5.814864562081468e-11</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0002183283068006858</v>
+        <v>6.427250398566287e-11</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.000179987633600831</v>
+        <v>2.262295351052046e-10</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0002412924804957584</v>
+        <v>1.012656972165793e-12</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0003479516017250717</v>
+        <v>1.067883073635478e-10</v>
       </c>
       <c r="DD17" t="n">
-        <v>7.603409358125646e-06</v>
+        <v>1.054242942943873e-10</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.0005238026496954262</v>
+        <v>4.168825701311718e-11</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0006508718943223357</v>
+        <v>3.748274746140368e-10</v>
       </c>
       <c r="DG17" t="n">
-        <v>5.246531509328634e-05</v>
+        <v>3.741793264122606e-10</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.001977031817659736</v>
+        <v>2.001010329655273e-10</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.001065439661033452</v>
+        <v>1.611688560387847e-10</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.0002703523787204176</v>
+        <v>1.136720162442373e-10</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0005639686132781208</v>
+        <v>2.228886519795026e-10</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0002065541048068553</v>
+        <v>6.065955376888255e-11</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0003551821573637426</v>
+        <v>3.861537825611272e-11</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0003250412410125136</v>
+        <v>2.609717442147996e-10</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.0003017034323420376</v>
+        <v>2.375999397230544e-10</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0005711772246286273</v>
+        <v>3.99289004637815e-11</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0004107607528567314</v>
+        <v>1.72780192930766e-10</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0004267902404535562</v>
+        <v>1.205553851191254e-10</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0002152969245798886</v>
+        <v>1.189504883480907e-10</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0002094184892484918</v>
+        <v>1.750908446007671e-10</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.0001920658542076126</v>
+        <v>1.103486607645365e-10</v>
       </c>
       <c r="DV17" t="n">
-        <v>5.475203943205997e-05</v>
+        <v>2.247063368709945e-10</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0001644006406422704</v>
+        <v>1.486741008083214e-10</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0004748940991703421</v>
+        <v>6.725448670197309e-11</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.825233867857605e-05</v>
+        <v>1.758951040375933e-10</v>
       </c>
       <c r="DZ17" t="n">
-        <v>8.970191993284971e-05</v>
+        <v>8.837658382887525e-11</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0005935552180744708</v>
+        <v>5.14027154174812e-10</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0001790811365935951</v>
+        <v>2.366816742593869e-10</v>
       </c>
       <c r="EC17" t="n">
-        <v>9.13669791771099e-05</v>
+        <v>3.486894661897111e-10</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0001195172662846744</v>
+        <v>4.405320205846941e-11</v>
       </c>
       <c r="EE17" t="n">
-        <v>4.042358341393992e-06</v>
+        <v>4.058056841949043e-12</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0005967990728095174</v>
+        <v>1.460298375277613e-11</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.001253570197150111</v>
+        <v>1.085770084952031e-10</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.0001913908490678295</v>
+        <v>8.540047835570164e-11</v>
       </c>
       <c r="EI17" t="n">
-        <v>8.722973143449053e-05</v>
+        <v>1.068982263818796e-10</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0002418204967398196</v>
+        <v>1.798316703882641e-11</v>
       </c>
       <c r="EK17" t="n">
-        <v>5.809215872432105e-05</v>
+        <v>1.106946270756914e-10</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0001609788741916418</v>
+        <v>6.349390457849324e-11</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0002199082373408601</v>
+        <v>8.488782593518707e-11</v>
       </c>
       <c r="EN17" t="n">
-        <v>3.959932291763835e-05</v>
+        <v>9.974954889857557e-11</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0002168589999200776</v>
+        <v>5.904117472699255e-11</v>
       </c>
       <c r="EP17" t="n">
-        <v>7.405025826301426e-05</v>
+        <v>1.521197473541847e-10</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0004423432983458042</v>
+        <v>6.116260276023411e-11</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0002302950160810724</v>
+        <v>2.910285901158716e-11</v>
       </c>
       <c r="ES17" t="n">
-        <v>7.121325324987993e-05</v>
+        <v>2.135892851473642e-10</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.0004635045188479125</v>
+        <v>2.277973226716412e-10</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0003447415074333549</v>
+        <v>3.757983507712837e-11</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0009067165665328503</v>
+        <v>6.192208551469847e-11</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0005168516072444618</v>
+        <v>5.613906908785715e-11</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.00020006881095469</v>
+        <v>6.225641530077652e-11</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.0008944897563196719</v>
+        <v>2.262243725681401e-10</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.0002752671716734767</v>
+        <v>2.742219992746264e-11</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0002048621536232531</v>
+        <v>7.89517201615908e-11</v>
       </c>
       <c r="FB17" t="n">
-        <v>2.56908515439136e-05</v>
+        <v>1.067838040214042e-10</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0002220598398707807</v>
+        <v>2.141253285792288e-10</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.0003616097965277731</v>
+        <v>6.652126766093502e-11</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0001761477033142</v>
+        <v>1.448636904877176e-10</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.0001342935720458627</v>
+        <v>4.474133216691989e-11</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0002327393740415573</v>
+        <v>4.938929820674787e-11</v>
       </c>
       <c r="FH17" t="n">
-        <v>7.617331721121445e-05</v>
+        <v>1.304045066374826e-10</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0003430568613111973</v>
+        <v>3.265999692914079e-10</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0009686864214017987</v>
+        <v>2.417133160292906e-11</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0005795203032903373</v>
+        <v>3.350044963656984e-10</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.0004534214967861772</v>
+        <v>1.083372350163536e-10</v>
       </c>
       <c r="FM17" t="n">
-        <v>3.987083618994802e-05</v>
+        <v>4.784382959255318e-11</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0001442464417777956</v>
+        <v>2.588733116759556e-10</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0006410012720152736</v>
+        <v>1.625325429799318e-10</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0009353606146760285</v>
+        <v>2.448636016172401e-10</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0009214926394633949</v>
+        <v>4.304793743692414e-10</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0008270975667983294</v>
+        <v>6.196484991782825e-10</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0002423790865577757</v>
+        <v>3.97654020822813e-10</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0001743342872941867</v>
+        <v>1.668545440702829e-10</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0003871133667416871</v>
+        <v>6.093529847372992e-11</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0001478217454859987</v>
+        <v>1.493835471988447e-10</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0001632447965675965</v>
+        <v>2.40331032852481e-10</v>
       </c>
       <c r="FX17" t="n">
-        <v>3.599657429731451e-05</v>
+        <v>1.512806824255364e-10</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0008112962241284549</v>
+        <v>1.128203433453656e-11</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0002262651978526264</v>
+        <v>2.119643349729472e-10</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0001037994152284227</v>
+        <v>2.646443619802596e-10</v>
       </c>
       <c r="GB17" t="n">
-        <v>7.840098987799138e-05</v>
+        <v>1.941168892294343e-10</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0004117109056096524</v>
+        <v>4.083400839682838e-10</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0007938856142573059</v>
+        <v>2.627098816265772e-10</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.001036171684972942</v>
+        <v>9.644891829641011e-11</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0004344294720795006</v>
+        <v>1.420895068271477e-10</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0003023425815626979</v>
+        <v>2.757439936107442e-11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.058714380837046e-05</v>
+        <v>0.0005475124344229698</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0009866023901849985</v>
+        <v>0.008823378011584282</v>
       </c>
       <c r="C18" t="n">
-        <v>4.456725582713261e-05</v>
+        <v>0.001908156787976623</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0006171261193230748</v>
+        <v>0.006176161579787731</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0001197730598505586</v>
+        <v>0.0005996848922222853</v>
       </c>
       <c r="F18" t="n">
-        <v>8.669677481520921e-05</v>
+        <v>0.01316423993557692</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0001150008174590766</v>
+        <v>0.003502516308799386</v>
       </c>
       <c r="H18" t="n">
-        <v>4.820261892746203e-05</v>
+        <v>0.00300425523892045</v>
       </c>
       <c r="I18" t="n">
-        <v>5.167737981537357e-05</v>
+        <v>0.002183638978749514</v>
       </c>
       <c r="J18" t="n">
-        <v>7.600997196277604e-05</v>
+        <v>0.0006422032020054758</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0008762187790125608</v>
+        <v>0.009721655398607254</v>
       </c>
       <c r="L18" t="n">
-        <v>2.135581235052086e-05</v>
+        <v>0.003368637524545193</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0005674986750818789</v>
+        <v>0.00789475254714489</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0001662725262576714</v>
+        <v>0.003818545956164598</v>
       </c>
       <c r="O18" t="n">
-        <v>1.592583976162132e-05</v>
+        <v>0.01366297155618668</v>
       </c>
       <c r="P18" t="n">
-        <v>7.592232577735558e-05</v>
+        <v>0.002156909089535475</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0001201984123326838</v>
+        <v>0.002867753617465496</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36018843477359e-06</v>
+        <v>0.0007285678293555975</v>
       </c>
       <c r="S18" t="n">
-        <v>6.824116280768067e-05</v>
+        <v>0.0003927446960005909</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0001161544423666783</v>
+        <v>9.818136459216475e-05</v>
       </c>
       <c r="U18" t="n">
-        <v>6.736408977303654e-06</v>
+        <v>0.000882859923876822</v>
       </c>
       <c r="V18" t="n">
-        <v>6.401594146154821e-05</v>
+        <v>0.0009976733708754182</v>
       </c>
       <c r="W18" t="n">
-        <v>6.387772009475157e-05</v>
+        <v>0.0002682059421204031</v>
       </c>
       <c r="X18" t="n">
-        <v>2.223954652436078e-05</v>
+        <v>0.002294214908033609</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.17009892873466e-05</v>
+        <v>0.001264995662495494</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.681331044295803e-05</v>
+        <v>0.001083155977539718</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.83682441781275e-05</v>
+        <v>0.0004038460610900074</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.936501399148256e-05</v>
+        <v>0.001077996334061027</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0001953913451870903</v>
+        <v>0.0009851752547547221</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.184344182547648e-05</v>
+        <v>0.002241421025246382</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.813059498090297e-05</v>
+        <v>0.00171721784863621</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.088466317218263e-05</v>
+        <v>0.001422866247594357</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.574593418103177e-05</v>
+        <v>0.004208620637655258</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.345196015900001e-05</v>
+        <v>0.0005980970454402268</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.535775663796812e-05</v>
+        <v>0.004694585688412189</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.597034083213657e-05</v>
+        <v>0.0001632433995837346</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.541487447160762e-05</v>
+        <v>0.001288525527343154</v>
       </c>
       <c r="AL18" t="n">
-        <v>9.909516666084528e-05</v>
+        <v>0.002041961066424847</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.228367455041735e-05</v>
+        <v>0.001601041993126273</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.78607003565412e-05</v>
+        <v>0.001073729712516069</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.777678158367053e-05</v>
+        <v>0.0005343595985323191</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.297202344285324e-05</v>
+        <v>0.0006735683418810368</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.489058771170676e-05</v>
+        <v>0.0004442062345333397</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.443620360281784e-05</v>
+        <v>0.0006151674897409976</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.496191336831544e-05</v>
+        <v>0.001433438039384782</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.0001037472247844562</v>
+        <v>0.0005919579416513443</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0006030232179909945</v>
+        <v>0.004419606178998947</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.0001331372477579862</v>
+        <v>0.00281904824078083</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.000193000043509528</v>
+        <v>0.00216713547706604</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.091126563958824e-05</v>
+        <v>0.008539697155356407</v>
       </c>
       <c r="AY18" t="n">
-        <v>6.489126826636493e-05</v>
+        <v>0.006911150179803371</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.632712130434811e-05</v>
+        <v>0.0004893761943094432</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.344619446783327e-05</v>
+        <v>0.001263384008780122</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.670444882824086e-05</v>
+        <v>0.0002192543906858191</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.848256139666773e-05</v>
+        <v>0.0001342208270216361</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.0001437909522792324</v>
+        <v>0.00205190060660243</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.0001712354278424755</v>
+        <v>0.002242960967123508</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.0001049090351443738</v>
+        <v>0.001632978091947734</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.000108077801996842</v>
+        <v>0.003946074284613132</v>
       </c>
       <c r="BH18" t="n">
-        <v>2.874144047382288e-05</v>
+        <v>0.002923223422840238</v>
       </c>
       <c r="BI18" t="n">
-        <v>6.239317735889927e-05</v>
+        <v>0.001096024876460433</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.0001232745125889778</v>
+        <v>0.003081013448536396</v>
       </c>
       <c r="BK18" t="n">
-        <v>2.83333192783175e-05</v>
+        <v>0.0005288302199915051</v>
       </c>
       <c r="BL18" t="n">
-        <v>8.444831473752856e-05</v>
+        <v>5.047575905336998e-05</v>
       </c>
       <c r="BM18" t="n">
-        <v>4.08679261454381e-05</v>
+        <v>0.0006788767641410232</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.92580288159661e-05</v>
+        <v>6.794737419113517e-05</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.666246266220696e-05</v>
+        <v>0.002264149952679873</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.0001548287982586771</v>
+        <v>0.0003197830519638956</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.841438461269718e-05</v>
+        <v>0.001804353436455131</v>
       </c>
       <c r="BR18" t="n">
-        <v>3.56006421498023e-05</v>
+        <v>0.0006300853565335274</v>
       </c>
       <c r="BS18" t="n">
-        <v>4.315821206546389e-05</v>
+        <v>0.001342007308267057</v>
       </c>
       <c r="BT18" t="n">
-        <v>7.249508053064346e-05</v>
+        <v>0.001792173599824309</v>
       </c>
       <c r="BU18" t="n">
-        <v>7.311454100999981e-05</v>
+        <v>0.0003481527091935277</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.0003154189616907388</v>
+        <v>0.002788952318951488</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.389087841147557e-05</v>
+        <v>0.0009166655363515019</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.000134873014758341</v>
+        <v>0.002364033833146095</v>
       </c>
       <c r="BY18" t="n">
-        <v>6.045097688911483e-05</v>
+        <v>0.002112470101565123</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1.657731445448007e-05</v>
+        <v>0.003797363955527544</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.772068132297136e-05</v>
+        <v>0.001971497898921371</v>
       </c>
       <c r="CB18" t="n">
-        <v>1.169232291431399e-05</v>
+        <v>0.001094981678761542</v>
       </c>
       <c r="CC18" t="n">
-        <v>6.575268344022334e-05</v>
+        <v>0.001061495626345277</v>
       </c>
       <c r="CD18" t="n">
-        <v>1.539772893011104e-05</v>
+        <v>0.0004785011988133192</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.000168110229424201</v>
+        <v>0.002599111991003156</v>
       </c>
       <c r="CF18" t="n">
-        <v>3.902295793523081e-05</v>
+        <v>0.0004394197021611035</v>
       </c>
       <c r="CG18" t="n">
-        <v>7.015892333583906e-05</v>
+        <v>0.002042599022388458</v>
       </c>
       <c r="CH18" t="n">
-        <v>3.558414755389094e-05</v>
+        <v>0.0001534279290353879</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.914233325805981e-05</v>
+        <v>0.003176635829731822</v>
       </c>
       <c r="CJ18" t="n">
-        <v>2.411348577879835e-05</v>
+        <v>4.200093826511875e-05</v>
       </c>
       <c r="CK18" t="n">
-        <v>4.792635081685148e-06</v>
+        <v>0.0009768196614459157</v>
       </c>
       <c r="CL18" t="n">
-        <v>2.35413208429236e-05</v>
+        <v>0.001617357367649674</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.0002234408457297832</v>
+        <v>0.001359326648525894</v>
       </c>
       <c r="CN18" t="n">
-        <v>4.454784721019678e-05</v>
+        <v>0.000733843189664185</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.845657243393362e-05</v>
+        <v>0.003558741183951497</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.0001562289835419506</v>
+        <v>0.002618294209241867</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0001793158007785678</v>
+        <v>0.004037149250507355</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.0001103037866414525</v>
+        <v>0.001056471024639904</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.0001238895347341895</v>
+        <v>0.0004895063466392457</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.000167143385624513</v>
+        <v>0.0008007293799892068</v>
       </c>
       <c r="CU18" t="n">
-        <v>3.422963345656171e-06</v>
+        <v>0.00135025754570961</v>
       </c>
       <c r="CV18" t="n">
-        <v>4.462381639314117e-06</v>
+        <v>0.0006717949872836471</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.0001692528312560171</v>
+        <v>0.00256106024608016</v>
       </c>
       <c r="CX18" t="n">
-        <v>6.75083720125258e-05</v>
+        <v>0.0006506913341581821</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.000101805584563408</v>
+        <v>0.00231688329949975</v>
       </c>
       <c r="CZ18" t="n">
-        <v>3.780703627853654e-05</v>
+        <v>0.0008038936066441238</v>
       </c>
       <c r="DA18" t="n">
-        <v>4.079496193298837e-06</v>
+        <v>0.003514833515509963</v>
       </c>
       <c r="DB18" t="n">
-        <v>3.043870128749404e-05</v>
+        <v>0.000202026276383549</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.806661202863324e-05</v>
+        <v>0.0009962724288925529</v>
       </c>
       <c r="DD18" t="n">
-        <v>8.83587563293986e-06</v>
+        <v>0.001248811604455113</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.00012885921751149</v>
+        <v>0.001768964342772961</v>
       </c>
       <c r="DF18" t="n">
-        <v>9.389823389938101e-05</v>
+        <v>0.003395537380129099</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.988440999411978e-06</v>
+        <v>0.00212015793658793</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.0002003082481678575</v>
+        <v>0.001571991830132902</v>
       </c>
       <c r="DI18" t="n">
-        <v>5.551990034291521e-05</v>
+        <v>0.001447455724701285</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.365374166402034e-05</v>
+        <v>0.004679310601204634</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.640472616301849e-05</v>
+        <v>0.0004849045362789184</v>
       </c>
       <c r="DL18" t="n">
-        <v>5.886787039344199e-05</v>
+        <v>0.002103542909026146</v>
       </c>
       <c r="DM18" t="n">
-        <v>2.441963442834094e-05</v>
+        <v>0.00193028140347451</v>
       </c>
       <c r="DN18" t="n">
-        <v>2.342845982639119e-05</v>
+        <v>0.001440029358491302</v>
       </c>
       <c r="DO18" t="n">
-        <v>6.973365088924766e-05</v>
+        <v>0.002128870226442814</v>
       </c>
       <c r="DP18" t="n">
-        <v>5.043987039243802e-05</v>
+        <v>0.0009467109339311719</v>
       </c>
       <c r="DQ18" t="n">
-        <v>5.389799116528593e-05</v>
+        <v>0.001194258918985724</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.0001247401523869485</v>
+        <v>0.0005156163824722171</v>
       </c>
       <c r="DS18" t="n">
-        <v>9.549231435812544e-06</v>
+        <v>0.000716020877007395</v>
       </c>
       <c r="DT18" t="n">
-        <v>1.45676867759903e-05</v>
+        <v>0.001072788378223777</v>
       </c>
       <c r="DU18" t="n">
-        <v>4.600985266733915e-05</v>
+        <v>0.001817385433241725</v>
       </c>
       <c r="DV18" t="n">
-        <v>4.964384788763709e-05</v>
+        <v>0.001273415051400661</v>
       </c>
       <c r="DW18" t="n">
-        <v>6.240425136638805e-05</v>
+        <v>0.0009840612765401602</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.000141421114676632</v>
+        <v>2.046097506536171e-05</v>
       </c>
       <c r="DY18" t="n">
-        <v>1.8121683751815e-05</v>
+        <v>0.003303293604403734</v>
       </c>
       <c r="DZ18" t="n">
-        <v>6.485759513452649e-05</v>
+        <v>0.0002311880816705525</v>
       </c>
       <c r="EA18" t="n">
-        <v>5.987809345242567e-05</v>
+        <v>0.001490572467446327</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.759539190970827e-05</v>
+        <v>0.0008847626158967614</v>
       </c>
       <c r="EC18" t="n">
-        <v>4.277492189430632e-05</v>
+        <v>0.000655912677757442</v>
       </c>
       <c r="ED18" t="n">
-        <v>9.075358320842497e-06</v>
+        <v>0.002576330676674843</v>
       </c>
       <c r="EE18" t="n">
-        <v>1.131295357481577e-05</v>
+        <v>0.002221991075202823</v>
       </c>
       <c r="EF18" t="n">
-        <v>2.324714478163514e-05</v>
+        <v>0.0006461078301072121</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.0001219745608977973</v>
+        <v>0.001382737653329968</v>
       </c>
       <c r="EH18" t="n">
-        <v>8.0105361121241e-05</v>
+        <v>0.001896741101518273</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.0001091891099349596</v>
+        <v>0.001006520702503622</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.0001343280600849539</v>
+        <v>0.001407909556291997</v>
       </c>
       <c r="EK18" t="n">
-        <v>4.434493348526303e-06</v>
+        <v>0.002321783220395446</v>
       </c>
       <c r="EL18" t="n">
-        <v>2.397709431534167e-05</v>
+        <v>0.0005828192224726081</v>
       </c>
       <c r="EM18" t="n">
-        <v>3.24309803545475e-05</v>
+        <v>0.0007354198605753481</v>
       </c>
       <c r="EN18" t="n">
-        <v>1.993652040255256e-05</v>
+        <v>0.0009256673511117697</v>
       </c>
       <c r="EO18" t="n">
-        <v>1.328662619926035e-07</v>
+        <v>0.0005565554602071643</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.0001928494602907449</v>
+        <v>0.001493731630034745</v>
       </c>
       <c r="EQ18" t="n">
-        <v>9.268540452467278e-05</v>
+        <v>0.001314126886427402</v>
       </c>
       <c r="ER18" t="n">
-        <v>6.527938967337832e-05</v>
+        <v>0.001512611750513315</v>
       </c>
       <c r="ES18" t="n">
-        <v>3.212432056898251e-05</v>
+        <v>0.001181481988169253</v>
       </c>
       <c r="ET18" t="n">
-        <v>2.09929912671214e-05</v>
+        <v>0.0003759206156246364</v>
       </c>
       <c r="EU18" t="n">
-        <v>7.547536370111629e-05</v>
+        <v>0.0004672157228924334</v>
       </c>
       <c r="EV18" t="n">
-        <v>4.480478310142644e-05</v>
+        <v>0.001296358881518245</v>
       </c>
       <c r="EW18" t="n">
-        <v>3.683211252791807e-05</v>
+        <v>0.002072998555377126</v>
       </c>
       <c r="EX18" t="n">
-        <v>3.301293327240273e-05</v>
+        <v>0.00071213289629668</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.0001771846582414582</v>
+        <v>0.003159843385219574</v>
       </c>
       <c r="EZ18" t="n">
-        <v>4.620844993041828e-05</v>
+        <v>0.0003293557674624026</v>
       </c>
       <c r="FA18" t="n">
-        <v>8.301632624352351e-05</v>
+        <v>0.002511363010853529</v>
       </c>
       <c r="FB18" t="n">
-        <v>2.41766592807835e-05</v>
+        <v>1.745301779010333e-05</v>
       </c>
       <c r="FC18" t="n">
-        <v>7.571634341729805e-07</v>
+        <v>0.002916254801675677</v>
       </c>
       <c r="FD18" t="n">
-        <v>2.499610855011269e-05</v>
+        <v>2.33584432862699e-05</v>
       </c>
       <c r="FE18" t="n">
-        <v>2.552679688960779e-06</v>
+        <v>0.0008509992039762437</v>
       </c>
       <c r="FF18" t="n">
-        <v>1.963186514331028e-05</v>
+        <v>0.0006690581212751567</v>
       </c>
       <c r="FG18" t="n">
-        <v>2.297506580362096e-05</v>
+        <v>0.0003480054438114166</v>
       </c>
       <c r="FH18" t="n">
-        <v>8.760490891290829e-05</v>
+        <v>0.002164471196010709</v>
       </c>
       <c r="FI18" t="n">
-        <v>8.097208046820015e-05</v>
+        <v>0.003254947485402226</v>
       </c>
       <c r="FJ18" t="n">
-        <v>6.634354213019833e-05</v>
+        <v>0.002560034394264221</v>
       </c>
       <c r="FK18" t="n">
-        <v>6.755127833457664e-05</v>
+        <v>0.0006257204222492874</v>
       </c>
       <c r="FL18" t="n">
-        <v>3.343030039104633e-05</v>
+        <v>0.004554367158561945</v>
       </c>
       <c r="FM18" t="n">
-        <v>2.439192030578852e-05</v>
+        <v>6.969229434616864e-05</v>
       </c>
       <c r="FN18" t="n">
-        <v>2.715006485232152e-05</v>
+        <v>0.002324848901480436</v>
       </c>
       <c r="FO18" t="n">
-        <v>2.335617500648368e-05</v>
+        <v>0.003492617513984442</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.0001043900119839236</v>
+        <v>0.001500427257269621</v>
       </c>
       <c r="FQ18" t="n">
-        <v>4.411645568325184e-05</v>
+        <v>0.0009535991121083498</v>
       </c>
       <c r="FR18" t="n">
-        <v>0.0001440420746803284</v>
+        <v>0.005923353601247072</v>
       </c>
       <c r="FS18" t="n">
-        <v>5.019141099182889e-06</v>
+        <v>0.001579211791977286</v>
       </c>
       <c r="FT18" t="n">
-        <v>7.356984497164376e-06</v>
+        <v>0.001804167055524886</v>
       </c>
       <c r="FU18" t="n">
-        <v>9.261511149816215e-05</v>
+        <v>0.002435705391690135</v>
       </c>
       <c r="FV18" t="n">
-        <v>2.017623592109885e-05</v>
+        <v>0.0008636143174953759</v>
       </c>
       <c r="FW18" t="n">
-        <v>3.709663724293932e-05</v>
+        <v>0.002795486943796277</v>
       </c>
       <c r="FX18" t="n">
-        <v>4.451838321983814e-05</v>
+        <v>0.001709638745523989</v>
       </c>
       <c r="FY18" t="n">
-        <v>9.112866246141493e-05</v>
+        <v>0.0002916593512054533</v>
       </c>
       <c r="FZ18" t="n">
-        <v>1.549049193272367e-05</v>
+        <v>0.001452957163564861</v>
       </c>
       <c r="GA18" t="n">
-        <v>5.062611671746708e-05</v>
+        <v>0.002749990904703736</v>
       </c>
       <c r="GB18" t="n">
-        <v>2.993959788000211e-05</v>
+        <v>0.0009107612422667444</v>
       </c>
       <c r="GC18" t="n">
-        <v>1.314523069595452e-05</v>
+        <v>0.006003934424370527</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.0001151762844529003</v>
+        <v>0.005575411487370729</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.0001972179743461311</v>
+        <v>0.0008468825253657997</v>
       </c>
       <c r="GF18" t="n">
-        <v>3.116689913440496e-05</v>
+        <v>0.000721051765140146</v>
       </c>
       <c r="GG18" t="n">
-        <v>7.787378126522526e-05</v>
+        <v>0.0005718914908356965</v>
       </c>
     </row>
     <row r="19">
@@ -11241,571 +11241,571 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8.153043745551258e-05</v>
+        <v>0.1167784035205841</v>
       </c>
       <c r="B20" t="n">
-        <v>0.003475620644167066</v>
+        <v>0.4109968841075897</v>
       </c>
       <c r="C20" t="n">
-        <v>7.31020190869458e-05</v>
+        <v>0.04624879732728004</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00107965525239706</v>
+        <v>0.06781882047653198</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000738389091566205</v>
+        <v>0.2505896389484406</v>
       </c>
       <c r="F20" t="n">
-        <v>0.001429045805707574</v>
+        <v>0.1726661324501038</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0004112602618988603</v>
+        <v>0.1451172977685928</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001133183599449694</v>
+        <v>0.1595468372106552</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0006260884110815823</v>
+        <v>0.2569265365600586</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0005953273503109813</v>
+        <v>0.1170490011572838</v>
       </c>
       <c r="K20" t="n">
-        <v>0.003055971348658204</v>
+        <v>0.5778017044067383</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0002456163638271391</v>
+        <v>0.01162795536220074</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0004427119856700301</v>
+        <v>0.252984493970871</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0001459080813219771</v>
+        <v>0.1702937930822372</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00178953749127686</v>
+        <v>0.1553368419408798</v>
       </c>
       <c r="P20" t="n">
-        <v>0.0005202017491683364</v>
+        <v>0.1442825794219971</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.459411138668656e-05</v>
+        <v>0.05661804229021072</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0007471776916645467</v>
+        <v>0.2100709974765778</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0001608217426110059</v>
+        <v>0.01044661551713943</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0002526182506699115</v>
+        <v>0.08715641498565674</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0003081365721300244</v>
+        <v>0.02545581385493279</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0003347779274918139</v>
+        <v>0.1865131556987762</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0004795514978468418</v>
+        <v>0.1223261207342148</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0003482208703644574</v>
+        <v>0.05177201330661774</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0002416503848508</v>
+        <v>0.008956991136074066</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.0006584924994967878</v>
+        <v>0.06801671534776688</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.0004698206030298024</v>
+        <v>0.02490286901593208</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.0001624104043003172</v>
+        <v>0.01796473376452923</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.0001873312867246568</v>
+        <v>0.04746041819453239</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0002977538388222456</v>
+        <v>0.0233343280851841</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0001127685463870876</v>
+        <v>0.1786893010139465</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.0003115542931482196</v>
+        <v>0.2514139413833618</v>
       </c>
       <c r="AG20" t="n">
-        <v>9.341518307337537e-05</v>
+        <v>0.1521828025579453</v>
       </c>
       <c r="AH20" t="n">
-        <v>5.506776506081223e-05</v>
+        <v>0.009049169719219208</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.0004439088224899024</v>
+        <v>0.1562268733978271</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.0001001452546915971</v>
+        <v>0.09338054060935974</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.0004641771083697677</v>
+        <v>0.05333460122346878</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.0005355927860364318</v>
+        <v>0.1252607554197311</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.922118361922912e-05</v>
+        <v>0.04400226846337318</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.000147799146361649</v>
+        <v>0.1533300876617432</v>
       </c>
       <c r="AO20" t="n">
-        <v>4.252813596394844e-05</v>
+        <v>0.02396076545119286</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.0004354912089183927</v>
+        <v>0.01603959500789642</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.0002263356582261622</v>
+        <v>0.03763952851295471</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.0002774936147034168</v>
+        <v>0.1918636560440063</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.0004297738487366587</v>
+        <v>0.01656492799520493</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.829202513676137e-05</v>
+        <v>0.1345456391572952</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.002264845184981823</v>
+        <v>0.5631925463676453</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.0005460645188577473</v>
+        <v>0.0241903979331255</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.0003504250198602676</v>
+        <v>0.1888709366321564</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.0003412513178773224</v>
+        <v>0.03664050251245499</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.0008532890351489186</v>
+        <v>0.1173742935061455</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.0007423705537803471</v>
+        <v>0.05876385420560837</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.0006455878610722721</v>
+        <v>0.05155038088560104</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.0006363975116983056</v>
+        <v>0.03478825092315674</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.939211066812277e-05</v>
+        <v>0.05784003809094429</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.0007691241335123777</v>
+        <v>0.06534068286418915</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.0008923534769564867</v>
+        <v>0.0004615169018507004</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.0002737119793891907</v>
+        <v>0.01659981161355972</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.000174642467754893</v>
+        <v>0.05003850162029266</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.0005163059686310589</v>
+        <v>0.02657268196344376</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.0002167216007364914</v>
+        <v>0.1903656125068665</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.0005327627877704799</v>
+        <v>0.134371891617775</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.00041542062535882</v>
+        <v>0.142975315451622</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.0001827408996177837</v>
+        <v>0.04075378179550171</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.0002605878980830312</v>
+        <v>0.107510432600975</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.000363129423931241</v>
+        <v>0.03158716857433319</v>
       </c>
       <c r="BO20" t="n">
-        <v>8.713174611330032e-05</v>
+        <v>0.05513418465852737</v>
       </c>
       <c r="BP20" t="n">
-        <v>2.94028504868038e-05</v>
+        <v>0.04317202419042587</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.0002180162555305287</v>
+        <v>0.06525102257728577</v>
       </c>
       <c r="BR20" t="n">
-        <v>0.0004294584505259991</v>
+        <v>0.1500824987888336</v>
       </c>
       <c r="BS20" t="n">
-        <v>0.000111398876470048</v>
+        <v>0.03413652628660202</v>
       </c>
       <c r="BT20" t="n">
-        <v>0.0001659451518207788</v>
+        <v>0.04628884792327881</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.972864993149415e-05</v>
+        <v>0.05366117134690285</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.001246946048922837</v>
+        <v>0.318471759557724</v>
       </c>
       <c r="BW20" t="n">
-        <v>0.0003675366169773042</v>
+        <v>0.01216505654156208</v>
       </c>
       <c r="BX20" t="n">
-        <v>3.134974394924939e-05</v>
+        <v>0.1582812666893005</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.0002764226519502699</v>
+        <v>0.04933606088161469</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.0004191215266473591</v>
+        <v>0.1266701221466064</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.239986886503175e-05</v>
+        <v>0.04420836642384529</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.0001257985277334228</v>
+        <v>0.02899765223264694</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.0004661374841816723</v>
+        <v>0.06556722521781921</v>
       </c>
       <c r="CD20" t="n">
-        <v>5.100181442685425e-05</v>
+        <v>0.01918864995241165</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.0006262257229536772</v>
+        <v>0.1473773270845413</v>
       </c>
       <c r="CF20" t="n">
-        <v>0.0003285881830379367</v>
+        <v>0.03224994987249374</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.0002151223015971482</v>
+        <v>0.01347340270876884</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.0001194702563225292</v>
+        <v>0.000429052859544754</v>
       </c>
       <c r="CI20" t="n">
-        <v>7.398489833576605e-05</v>
+        <v>0.04695633053779602</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.0002292517892783508</v>
+        <v>0.0200503021478653</v>
       </c>
       <c r="CK20" t="n">
-        <v>0.0001326678320765495</v>
+        <v>0.03231089934706688</v>
       </c>
       <c r="CL20" t="n">
-        <v>0.0003583545912988484</v>
+        <v>0.07148510217666626</v>
       </c>
       <c r="CM20" t="n">
-        <v>0.0004817015142180026</v>
+        <v>0.06392045319080353</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.0004817630688194185</v>
+        <v>0.246640682220459</v>
       </c>
       <c r="CO20" t="n">
-        <v>0.0001473407173762098</v>
+        <v>0.04154534637928009</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.0008592132362537086</v>
+        <v>0.1187124103307724</v>
       </c>
       <c r="CQ20" t="n">
-        <v>0.0005278708413243294</v>
+        <v>0.1314001679420471</v>
       </c>
       <c r="CR20" t="n">
-        <v>0.0004090686561539769</v>
+        <v>0.08560758829116821</v>
       </c>
       <c r="CS20" t="n">
-        <v>0.0006902486202307045</v>
+        <v>0.004873479716479778</v>
       </c>
       <c r="CT20" t="n">
-        <v>0.000524751259945333</v>
+        <v>0.02606942504644394</v>
       </c>
       <c r="CU20" t="n">
-        <v>7.990214362507686e-05</v>
+        <v>0.1229733526706696</v>
       </c>
       <c r="CV20" t="n">
-        <v>5.52021010662429e-05</v>
+        <v>0.01688198000192642</v>
       </c>
       <c r="CW20" t="n">
-        <v>0.0005291368579491973</v>
+        <v>0.1252960115671158</v>
       </c>
       <c r="CX20" t="n">
-        <v>0.0003355216176714748</v>
+        <v>0.03706705197691917</v>
       </c>
       <c r="CY20" t="n">
-        <v>0.000413659552577883</v>
+        <v>0.01727365702390671</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0.0001768590009305626</v>
+        <v>0.04133978113532066</v>
       </c>
       <c r="DA20" t="n">
-        <v>6.107371882535517e-05</v>
+        <v>0.06669019162654877</v>
       </c>
       <c r="DB20" t="n">
-        <v>0.0002497613895684481</v>
+        <v>0.01579594425857067</v>
       </c>
       <c r="DC20" t="n">
-        <v>0.0002604143228381872</v>
+        <v>0.02974477037787437</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.0003059135051444173</v>
+        <v>0.0824868306517601</v>
       </c>
       <c r="DE20" t="n">
-        <v>0.000394676229916513</v>
+        <v>0.01201360300183296</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.0002832130994647741</v>
+        <v>0.01950905472040176</v>
       </c>
       <c r="DG20" t="n">
-        <v>4.315715341363102e-05</v>
+        <v>0.06249948963522911</v>
       </c>
       <c r="DH20" t="n">
-        <v>0.001631285645999014</v>
+        <v>0.04299795627593994</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.0008669724920764565</v>
+        <v>0.2534130811691284</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.001159523730166256</v>
+        <v>0.04133745282888412</v>
       </c>
       <c r="DK20" t="n">
-        <v>0.0005223337793722749</v>
+        <v>0.05263622850179672</v>
       </c>
       <c r="DL20" t="n">
-        <v>0.0005551115609705448</v>
+        <v>0.1349383443593979</v>
       </c>
       <c r="DM20" t="n">
-        <v>0.0006020250730216503</v>
+        <v>0.05382534116506577</v>
       </c>
       <c r="DN20" t="n">
-        <v>0.0001854960719356313</v>
+        <v>0.005558907054364681</v>
       </c>
       <c r="DO20" t="n">
-        <v>4.766117854160257e-06</v>
+        <v>0.08103532344102859</v>
       </c>
       <c r="DP20" t="n">
-        <v>0.0003492338582873344</v>
+        <v>0.005901941563934088</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0.0001101482921512797</v>
+        <v>0.144956111907959</v>
       </c>
       <c r="DR20" t="n">
-        <v>1.902408257592469e-06</v>
+        <v>0.02033074572682381</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.0001391483674524352</v>
+        <v>0.02100457437336445</v>
       </c>
       <c r="DT20" t="n">
-        <v>0.0002764716336969286</v>
+        <v>0.002867495641112328</v>
       </c>
       <c r="DU20" t="n">
-        <v>0.0002138233830919489</v>
+        <v>0.08890531957149506</v>
       </c>
       <c r="DV20" t="n">
-        <v>0.0002526120224501938</v>
+        <v>0.01700521446764469</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.0001583572739036754</v>
+        <v>0.07329682260751724</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.0002104490267811343</v>
+        <v>0.0001690010540187359</v>
       </c>
       <c r="DY20" t="n">
-        <v>0.0004864131333306432</v>
+        <v>0.1160835474729538</v>
       </c>
       <c r="DZ20" t="n">
-        <v>0.0002223165647592396</v>
+        <v>0.05452292412519455</v>
       </c>
       <c r="EA20" t="n">
-        <v>6.416747783077881e-05</v>
+        <v>0.07674086838960648</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.0002265140356030315</v>
+        <v>0.08199232816696167</v>
       </c>
       <c r="EC20" t="n">
-        <v>1.508599962107837e-05</v>
+        <v>0.06778406351804733</v>
       </c>
       <c r="ED20" t="n">
-        <v>0.0001283274468732998</v>
+        <v>0.1432731449604034</v>
       </c>
       <c r="EE20" t="n">
-        <v>0.0005487574962899089</v>
+        <v>0.2251032590866089</v>
       </c>
       <c r="EF20" t="n">
-        <v>0.0002120643621310592</v>
+        <v>0.03228046745061874</v>
       </c>
       <c r="EG20" t="n">
-        <v>0.0009133368730545044</v>
+        <v>0.01852163672447205</v>
       </c>
       <c r="EH20" t="n">
-        <v>3.543821367202327e-05</v>
+        <v>0.02975530177354813</v>
       </c>
       <c r="EI20" t="n">
-        <v>6.784965808037668e-05</v>
+        <v>0.05524975806474686</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.0004480790230445564</v>
+        <v>0.1086373776197433</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.0001711763616185635</v>
+        <v>0.01947341859340668</v>
       </c>
       <c r="EL20" t="n">
-        <v>0.0003094092535320669</v>
+        <v>0.05919202789664268</v>
       </c>
       <c r="EM20" t="n">
-        <v>3.674428444355726e-05</v>
+        <v>0.06126781180500984</v>
       </c>
       <c r="EN20" t="n">
-        <v>0.0001651004422456026</v>
+        <v>0.09178278595209122</v>
       </c>
       <c r="EO20" t="n">
-        <v>3.656238550320268e-05</v>
+        <v>0.07693487405776978</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.0002551807265263051</v>
+        <v>0.07972411811351776</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0.0007744453032501042</v>
+        <v>0.01176468562334776</v>
       </c>
       <c r="ER20" t="n">
-        <v>0.0007438409957103431</v>
+        <v>0.08355956524610519</v>
       </c>
       <c r="ES20" t="n">
-        <v>0.0004645500448532403</v>
+        <v>0.04088341444730759</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.0002704156213440001</v>
+        <v>0.05377838760614395</v>
       </c>
       <c r="EU20" t="n">
-        <v>0.0006362966960296035</v>
+        <v>0.05152419954538345</v>
       </c>
       <c r="EV20" t="n">
-        <v>0.0006512175896205008</v>
+        <v>0.05473785847425461</v>
       </c>
       <c r="EW20" t="n">
-        <v>8.113745570881292e-05</v>
+        <v>0.02979756519198418</v>
       </c>
       <c r="EX20" t="n">
-        <v>1.838523894548416e-05</v>
+        <v>0.007161185145378113</v>
       </c>
       <c r="EY20" t="n">
-        <v>0.000535500468686223</v>
+        <v>0.1567295044660568</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0.0002838920918293297</v>
+        <v>0.03512879461050034</v>
       </c>
       <c r="FA20" t="n">
-        <v>0.0001464377128286287</v>
+        <v>0.01565518975257874</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.0002086299355141819</v>
+        <v>0.07399865984916687</v>
       </c>
       <c r="FC20" t="n">
-        <v>8.628469367977232e-05</v>
+        <v>0.07222650945186615</v>
       </c>
       <c r="FD20" t="n">
-        <v>0.0004377941659186035</v>
+        <v>0.03515142947435379</v>
       </c>
       <c r="FE20" t="n">
-        <v>0.0002604076871648431</v>
+        <v>0.02826637029647827</v>
       </c>
       <c r="FF20" t="n">
-        <v>0.0004246577445883304</v>
+        <v>0.08941549807786942</v>
       </c>
       <c r="FG20" t="n">
-        <v>0.0001662899885559455</v>
+        <v>0.01824378222227097</v>
       </c>
       <c r="FH20" t="n">
-        <v>3.516658762237057e-05</v>
+        <v>0.1224639788269997</v>
       </c>
       <c r="FI20" t="n">
-        <v>0.0007499672938138247</v>
+        <v>0.04510177299380302</v>
       </c>
       <c r="FJ20" t="n">
-        <v>0.0003010205982718617</v>
+        <v>0.01283210515975952</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.0001266548642888665</v>
+        <v>0.03214867040514946</v>
       </c>
       <c r="FL20" t="n">
-        <v>0.0001752383832354099</v>
+        <v>0.08580112457275391</v>
       </c>
       <c r="FM20" t="n">
-        <v>0.0002981629513669759</v>
+        <v>0.1335624605417252</v>
       </c>
       <c r="FN20" t="n">
-        <v>0.0002524431911297143</v>
+        <v>0.1467871516942978</v>
       </c>
       <c r="FO20" t="n">
-        <v>0.000246103445533663</v>
+        <v>0.1199244111776352</v>
       </c>
       <c r="FP20" t="n">
-        <v>0.000244879862293601</v>
+        <v>0.0263960175216198</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.0003069716040045023</v>
+        <v>0.1876441091299057</v>
       </c>
       <c r="FR20" t="n">
-        <v>0.0007004642975516617</v>
+        <v>0.08598551154136658</v>
       </c>
       <c r="FS20" t="n">
-        <v>0.0005671463441103697</v>
+        <v>0.1458248198032379</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.0007643052958883345</v>
+        <v>0.07704980671405792</v>
       </c>
       <c r="FU20" t="n">
-        <v>0.0003262875834479928</v>
+        <v>0.2700804471969604</v>
       </c>
       <c r="FV20" t="n">
-        <v>0.0005349087296053767</v>
+        <v>0.1108552664518356</v>
       </c>
       <c r="FW20" t="n">
-        <v>9.82500787358731e-05</v>
+        <v>0.120037741959095</v>
       </c>
       <c r="FX20" t="n">
-        <v>0.0001760334416758269</v>
+        <v>0.1343919038772583</v>
       </c>
       <c r="FY20" t="n">
-        <v>0.0007830619579181075</v>
+        <v>0.08245321363210678</v>
       </c>
       <c r="FZ20" t="n">
-        <v>0.0002250848920084536</v>
+        <v>0.08077282458543777</v>
       </c>
       <c r="GA20" t="n">
-        <v>0.0002258459862787277</v>
+        <v>0.08435171842575073</v>
       </c>
       <c r="GB20" t="n">
-        <v>0.0001955795451067388</v>
+        <v>0.08486682176589966</v>
       </c>
       <c r="GC20" t="n">
-        <v>0.000274924241239205</v>
+        <v>0.06524226814508438</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.0004641708510462195</v>
+        <v>0.00792822428047657</v>
       </c>
       <c r="GE20" t="n">
-        <v>0.001046423800289631</v>
+        <v>0.08967996388673782</v>
       </c>
       <c r="GF20" t="n">
-        <v>0.0001224839506903663</v>
+        <v>0.01558602973818779</v>
       </c>
       <c r="GG20" t="n">
-        <v>0.0001465395180275664</v>
+        <v>0.1327211260795593</v>
       </c>
     </row>
     <row r="21">
